--- a/delivered.xlsx
+++ b/delivered.xlsx
@@ -60,10 +60,10 @@
     <t>YT8854296074323</t>
   </si>
   <si>
-    <t>21.06.27</t>
-  </si>
-  <si>
     <t>Track</t>
+  </si>
+  <si>
+    <t>12.06.26</t>
   </si>
 </sst>
 </file>
@@ -416,7 +416,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">

--- a/delivered.xlsx
+++ b/delivered.xlsx
@@ -16,63 +16,550 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="176">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>JT5470618661992</t>
-  </si>
-  <si>
-    <t>YT8853194416420</t>
-  </si>
-  <si>
-    <t>YT8854017781451</t>
-  </si>
-  <si>
-    <t>YT8854262631028</t>
-  </si>
-  <si>
-    <t>YT8853958978522</t>
-  </si>
-  <si>
-    <t>JT5469762707519</t>
-  </si>
-  <si>
-    <t>YT8853701433100</t>
-  </si>
-  <si>
-    <t>YT8854284949433</t>
-  </si>
-  <si>
-    <t>YT8854020595393</t>
-  </si>
-  <si>
-    <t>JT5470459023380</t>
-  </si>
-  <si>
-    <t>YT8853715300359</t>
-  </si>
-  <si>
-    <t>YT8854303191955</t>
-  </si>
-  <si>
-    <t>YT8854296074323</t>
-  </si>
-  <si>
     <t>Track</t>
   </si>
   <si>
-    <t>12.06.26</t>
+    <t>YT8877953717504</t>
+  </si>
+  <si>
+    <t>YT8878376042259</t>
+  </si>
+  <si>
+    <t>JT5496562912088</t>
+  </si>
+  <si>
+    <t>JT5495975576123</t>
+  </si>
+  <si>
+    <t>JT5496426856472</t>
+  </si>
+  <si>
+    <t>YT8877978258660</t>
+  </si>
+  <si>
+    <t>JT5496083260646</t>
+  </si>
+  <si>
+    <t>JT5496555809498</t>
+  </si>
+  <si>
+    <t>YT8878489431799</t>
+  </si>
+  <si>
+    <t>YT8878924839212</t>
+  </si>
+  <si>
+    <t>YT8877954257843</t>
+  </si>
+  <si>
+    <t>JT5496397100619</t>
+  </si>
+  <si>
+    <t>JT5496532028174</t>
+  </si>
+  <si>
+    <t>YT8877957922382</t>
+  </si>
+  <si>
+    <t>YT8878892869002</t>
+  </si>
+  <si>
+    <t>YT8878973794278</t>
+  </si>
+  <si>
+    <t>JT5496426439535</t>
+  </si>
+  <si>
+    <t>YT8878013142445</t>
+  </si>
+  <si>
+    <t>YT8878891266189</t>
+  </si>
+  <si>
+    <t>YT8878364185573</t>
+  </si>
+  <si>
+    <t>YT8878433846646</t>
+  </si>
+  <si>
+    <t>YT8878373344697</t>
+  </si>
+  <si>
+    <t>JT5496397081847</t>
+  </si>
+  <si>
+    <t>JT5497157488381</t>
+  </si>
+  <si>
+    <t>YT8879052026024</t>
+  </si>
+  <si>
+    <t>JT5496184190660</t>
+  </si>
+  <si>
+    <t>YT8878964260562</t>
+  </si>
+  <si>
+    <t>YT8878955638123</t>
+  </si>
+  <si>
+    <t>SF5197162197328</t>
+  </si>
+  <si>
+    <t>YT8878636869808</t>
+  </si>
+  <si>
+    <t>SF5197155647582</t>
+  </si>
+  <si>
+    <t>JT5496410411821</t>
+  </si>
+  <si>
+    <t>JT5496392281486</t>
+  </si>
+  <si>
+    <t>YT8877225732475</t>
+  </si>
+  <si>
+    <t>JT5495399331306</t>
+  </si>
+  <si>
+    <t>YT8877267471668</t>
+  </si>
+  <si>
+    <t>JT5496376810838</t>
+  </si>
+  <si>
+    <t>JT5496270516915</t>
+  </si>
+  <si>
+    <t>JT5495394393083</t>
+  </si>
+  <si>
+    <t>JT5496376872907</t>
+  </si>
+  <si>
+    <t>JT5496389040454</t>
+  </si>
+  <si>
+    <t>JT5495342616032</t>
+  </si>
+  <si>
+    <t>JT5495433647705</t>
+  </si>
+  <si>
+    <t>JT5496380854606</t>
+  </si>
+  <si>
+    <t>JT5495899178526</t>
+  </si>
+  <si>
+    <t>JT5495806308084</t>
+  </si>
+  <si>
+    <t>YT8878190975603</t>
+  </si>
+  <si>
+    <t>YT8878256195196</t>
+  </si>
+  <si>
+    <t>07.07.26</t>
+  </si>
+  <si>
+    <t>07.07.27</t>
+  </si>
+  <si>
+    <t>07.07.28</t>
+  </si>
+  <si>
+    <t>07.07.29</t>
+  </si>
+  <si>
+    <t>07.07.30</t>
+  </si>
+  <si>
+    <t>07.07.31</t>
+  </si>
+  <si>
+    <t>07.07.32</t>
+  </si>
+  <si>
+    <t>07.07.33</t>
+  </si>
+  <si>
+    <t>07.07.34</t>
+  </si>
+  <si>
+    <t>07.07.35</t>
+  </si>
+  <si>
+    <t>07.07.36</t>
+  </si>
+  <si>
+    <t>07.07.37</t>
+  </si>
+  <si>
+    <t>07.07.38</t>
+  </si>
+  <si>
+    <t>07.07.39</t>
+  </si>
+  <si>
+    <t>07.07.40</t>
+  </si>
+  <si>
+    <t>07.07.41</t>
+  </si>
+  <si>
+    <t>07.07.42</t>
+  </si>
+  <si>
+    <t>07.07.43</t>
+  </si>
+  <si>
+    <t>07.07.44</t>
+  </si>
+  <si>
+    <t>07.07.45</t>
+  </si>
+  <si>
+    <t>07.07.46</t>
+  </si>
+  <si>
+    <t>07.07.47</t>
+  </si>
+  <si>
+    <t>07.07.48</t>
+  </si>
+  <si>
+    <t>07.07.49</t>
+  </si>
+  <si>
+    <t>07.07.50</t>
+  </si>
+  <si>
+    <t>07.07.51</t>
+  </si>
+  <si>
+    <t>07.07.52</t>
+  </si>
+  <si>
+    <t>07.07.53</t>
+  </si>
+  <si>
+    <t>07.07.54</t>
+  </si>
+  <si>
+    <t>07.07.55</t>
+  </si>
+  <si>
+    <t>07.07.56</t>
+  </si>
+  <si>
+    <t>07.07.57</t>
+  </si>
+  <si>
+    <t>07.07.58</t>
+  </si>
+  <si>
+    <t>07.07.59</t>
+  </si>
+  <si>
+    <t>07.07.60</t>
+  </si>
+  <si>
+    <t>07.07.61</t>
+  </si>
+  <si>
+    <t>07.07.62</t>
+  </si>
+  <si>
+    <t>07.07.63</t>
+  </si>
+  <si>
+    <t>07.07.64</t>
+  </si>
+  <si>
+    <t>07.07.65</t>
+  </si>
+  <si>
+    <t>07.07.66</t>
+  </si>
+  <si>
+    <t>07.07.67</t>
+  </si>
+  <si>
+    <t>07.07.68</t>
+  </si>
+  <si>
+    <t>07.07.69</t>
+  </si>
+  <si>
+    <t>07.07.70</t>
+  </si>
+  <si>
+    <t>07.07.71</t>
+  </si>
+  <si>
+    <t>07.07.72</t>
+  </si>
+  <si>
+    <t>07.07.73</t>
+  </si>
+  <si>
+    <t>07.07.74</t>
+  </si>
+  <si>
+    <t>07.07.75</t>
+  </si>
+  <si>
+    <t>07.07.76</t>
+  </si>
+  <si>
+    <t>07.07.77</t>
+  </si>
+  <si>
+    <t>07.07.78</t>
+  </si>
+  <si>
+    <t>07.07.79</t>
+  </si>
+  <si>
+    <t>07.07.80</t>
+  </si>
+  <si>
+    <t>07.07.81</t>
+  </si>
+  <si>
+    <t>07.07.82</t>
+  </si>
+  <si>
+    <t>07.07.83</t>
+  </si>
+  <si>
+    <t>07.07.84</t>
+  </si>
+  <si>
+    <t>07.07.86</t>
+  </si>
+  <si>
+    <t>07.07.87</t>
+  </si>
+  <si>
+    <t>07.07.88</t>
+  </si>
+  <si>
+    <t>07.07.89</t>
+  </si>
+  <si>
+    <t>07.07.90</t>
+  </si>
+  <si>
+    <t>07.07.91</t>
+  </si>
+  <si>
+    <t>07.07.92</t>
+  </si>
+  <si>
+    <t>07.07.93</t>
+  </si>
+  <si>
+    <t>07.07.94</t>
+  </si>
+  <si>
+    <t>07.07.95</t>
+  </si>
+  <si>
+    <t>07.07.96</t>
+  </si>
+  <si>
+    <t>07.07.97</t>
+  </si>
+  <si>
+    <t>07.07.98</t>
+  </si>
+  <si>
+    <t>07.07.99</t>
+  </si>
+  <si>
+    <t>07.07.100</t>
+  </si>
+  <si>
+    <t>07.07.101</t>
+  </si>
+  <si>
+    <t>07.07.102</t>
+  </si>
+  <si>
+    <t>07.07.103</t>
+  </si>
+  <si>
+    <t>07.07.104</t>
+  </si>
+  <si>
+    <t>07.07.105</t>
+  </si>
+  <si>
+    <t>07.07.106</t>
+  </si>
+  <si>
+    <t>07.07.107</t>
+  </si>
+  <si>
+    <t>07.07.108</t>
+  </si>
+  <si>
+    <t>07.07.109</t>
+  </si>
+  <si>
+    <t>07.07.110</t>
+  </si>
+  <si>
+    <t>07.07.111</t>
+  </si>
+  <si>
+    <t>07.07.112</t>
+  </si>
+  <si>
+    <t>07.07.113</t>
+  </si>
+  <si>
+    <t>07.07.114</t>
+  </si>
+  <si>
+    <t>07.07.115</t>
+  </si>
+  <si>
+    <t>07.07.116</t>
+  </si>
+  <si>
+    <t>07.07.117</t>
+  </si>
+  <si>
+    <t>07.07.118</t>
+  </si>
+  <si>
+    <t>07.07.119</t>
+  </si>
+  <si>
+    <t>07.07.120</t>
+  </si>
+  <si>
+    <t>07.07.121</t>
+  </si>
+  <si>
+    <t>07.07.122</t>
+  </si>
+  <si>
+    <t>07.07.123</t>
+  </si>
+  <si>
+    <t>07.07.124</t>
+  </si>
+  <si>
+    <t>07.07.125</t>
+  </si>
+  <si>
+    <t>07.07.126</t>
+  </si>
+  <si>
+    <t>07.07.127</t>
+  </si>
+  <si>
+    <t>07.07.128</t>
+  </si>
+  <si>
+    <t>07.07.129</t>
+  </si>
+  <si>
+    <t>07.07.130</t>
+  </si>
+  <si>
+    <t>07.07.131</t>
+  </si>
+  <si>
+    <t>07.07.132</t>
+  </si>
+  <si>
+    <t>07.07.133</t>
+  </si>
+  <si>
+    <t>07.07.134</t>
+  </si>
+  <si>
+    <t>07.07.135</t>
+  </si>
+  <si>
+    <t>07.07.136</t>
+  </si>
+  <si>
+    <t>07.07.137</t>
+  </si>
+  <si>
+    <t>07.07.138</t>
+  </si>
+  <si>
+    <t>07.07.139</t>
+  </si>
+  <si>
+    <t>07.07.140</t>
+  </si>
+  <si>
+    <t>07.07.141</t>
+  </si>
+  <si>
+    <t>07.07.142</t>
+  </si>
+  <si>
+    <t>07.07.143</t>
+  </si>
+  <si>
+    <t>07.07.144</t>
+  </si>
+  <si>
+    <t>07.07.145</t>
+  </si>
+  <si>
+    <t>07.07.146</t>
+  </si>
+  <si>
+    <t>07.07.147</t>
+  </si>
+  <si>
+    <t>07.07.148</t>
+  </si>
+  <si>
+    <t>07.07.149</t>
+  </si>
+  <si>
+    <t>07.07.150</t>
+  </si>
+  <si>
+    <t>07.07.151</t>
+  </si>
+  <si>
+    <t>07.07.152</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,12 +586,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -408,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -416,213 +906,1018 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>79114287730818</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>79113721261163</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>79114199400506</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>79114203887940</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>777418407164674</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>79114287731046</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>79114114585570</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>9817311547938</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>777418210107128</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>777418540098081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>79114008929258</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>79114123496019</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>79011910916564</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <v>79114056552890</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <v>79011810156917</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>79114129226699</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <v>79114119950813</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <v>79113831226396</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <v>79114249344806</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <v>9817286636034</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <v>9817306833974</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <v>9817266811309</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <v>79114119952579</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <v>79113859937536</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <v>9817310662063</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <v>79113826114819</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <v>79114123512156</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <v>9817293577073</v>
+      </c>
+      <c r="B41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <v>79114123473093</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <v>79114114546115</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <v>465426010024137</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>9817293845966</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <v>79114224672451</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <v>9817310661010</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <v>79114096392960</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <v>777417680528740</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <v>79114114545731</v>
+      </c>
+      <c r="B54" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <v>79114123470502</v>
+      </c>
+      <c r="B55" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <v>79114158480850</v>
+      </c>
+      <c r="B56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>79114287730634</v>
+      </c>
+      <c r="B57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <v>79011815866016</v>
+      </c>
+      <c r="B58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <v>777418512271860</v>
+      </c>
+      <c r="B59" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>77419047733484</v>
+      </c>
+      <c r="B62" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>465430383814609</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>777419015424748</v>
+      </c>
+      <c r="B64" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>465429582994887</v>
+      </c>
+      <c r="B65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
+        <v>79114917851687</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B68" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>79114362617905</v>
+      </c>
+      <c r="B69" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>79114362826221</v>
+      </c>
+      <c r="B70" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>79114362855049</v>
+      </c>
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
+        <v>79114716195683</v>
+      </c>
+      <c r="B73" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
+        <v>465432952519118</v>
+      </c>
+      <c r="B74" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B77" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>79114362617905</v>
+      </c>
+      <c r="B79" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
+        <v>777419015424748</v>
+      </c>
+      <c r="B80" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A81" s="3">
+        <v>79114302102362</v>
+      </c>
+      <c r="B81" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>79114218356055</v>
+      </c>
+      <c r="B82" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>79012581856167</v>
+      </c>
+      <c r="B83" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>79114409063138</v>
+      </c>
+      <c r="B84" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>79114218396909</v>
+      </c>
+      <c r="B85" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>9817337232960</v>
+      </c>
+      <c r="B86" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>465426605460787</v>
+      </c>
+      <c r="B87" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B88" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>79114347075820</v>
+      </c>
+      <c r="B89" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B92" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>79114641590826</v>
+      </c>
+      <c r="B93" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B95" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B96" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>777419080528783</v>
+      </c>
+      <c r="B97" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B99" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>8265950000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>78591200000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>465206000000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="B100" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>9817298550257</v>
+      </c>
+      <c r="B101" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>9817338834087</v>
+      </c>
+      <c r="B102" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>79114351420184</v>
+      </c>
+      <c r="B103" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>79114523941757</v>
+      </c>
+      <c r="B104" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B105" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B106" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B109" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>465425273153619</v>
+      </c>
+      <c r="B110" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>79114272667800</v>
+      </c>
+      <c r="B112" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>79114445687079</v>
+      </c>
+      <c r="B113" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>777419340694859</v>
+      </c>
+      <c r="B114" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>777419197107227</v>
+      </c>
+      <c r="B116" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>777419193134582</v>
+      </c>
+      <c r="B117" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>777419149591288</v>
+      </c>
+      <c r="B118" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>465427544369324</v>
+      </c>
+      <c r="B120" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B122" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>435227038851000</v>
+      </c>
+      <c r="B123" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B125" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>78590600000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>9815110000000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>78590500000000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>9815100000000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>9815060000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>777395000000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>9815140000000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>465207000000000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>9815040000000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>465204000000000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>9815130000000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>78590700000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>9815140000000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>78590700000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>9815120000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>8266470000000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>777395000000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>78590500000000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>777396000000000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>78591100000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>78590900000000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>777395000000000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>465212000000000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>465211000000000</v>
+      <c r="B127" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/delivered.xlsx
+++ b/delivered.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="167">
   <si>
     <t>Date</t>
   </si>
@@ -171,386 +171,359 @@
     <t>07.07.26</t>
   </si>
   <si>
-    <t>07.07.27</t>
-  </si>
-  <si>
-    <t>07.07.28</t>
-  </si>
-  <si>
-    <t>07.07.29</t>
-  </si>
-  <si>
-    <t>07.07.30</t>
-  </si>
-  <si>
-    <t>07.07.31</t>
-  </si>
-  <si>
-    <t>07.07.32</t>
-  </si>
-  <si>
-    <t>07.07.33</t>
-  </si>
-  <si>
-    <t>07.07.34</t>
-  </si>
-  <si>
-    <t>07.07.35</t>
-  </si>
-  <si>
-    <t>07.07.36</t>
-  </si>
-  <si>
-    <t>07.07.37</t>
-  </si>
-  <si>
-    <t>07.07.38</t>
-  </si>
-  <si>
-    <t>07.07.39</t>
-  </si>
-  <si>
-    <t>07.07.40</t>
-  </si>
-  <si>
-    <t>07.07.41</t>
-  </si>
-  <si>
-    <t>07.07.42</t>
-  </si>
-  <si>
-    <t>07.07.43</t>
-  </si>
-  <si>
-    <t>07.07.44</t>
-  </si>
-  <si>
-    <t>07.07.45</t>
-  </si>
-  <si>
-    <t>07.07.46</t>
-  </si>
-  <si>
-    <t>07.07.47</t>
-  </si>
-  <si>
-    <t>07.07.48</t>
-  </si>
-  <si>
-    <t>07.07.49</t>
-  </si>
-  <si>
-    <t>07.07.50</t>
-  </si>
-  <si>
-    <t>07.07.51</t>
-  </si>
-  <si>
-    <t>07.07.52</t>
-  </si>
-  <si>
-    <t>07.07.53</t>
-  </si>
-  <si>
-    <t>07.07.54</t>
-  </si>
-  <si>
-    <t>07.07.55</t>
-  </si>
-  <si>
-    <t>07.07.56</t>
-  </si>
-  <si>
-    <t>07.07.57</t>
-  </si>
-  <si>
-    <t>07.07.58</t>
-  </si>
-  <si>
-    <t>07.07.59</t>
-  </si>
-  <si>
-    <t>07.07.60</t>
-  </si>
-  <si>
-    <t>07.07.61</t>
-  </si>
-  <si>
-    <t>07.07.62</t>
-  </si>
-  <si>
-    <t>07.07.63</t>
-  </si>
-  <si>
-    <t>07.07.64</t>
-  </si>
-  <si>
-    <t>07.07.65</t>
-  </si>
-  <si>
-    <t>07.07.66</t>
-  </si>
-  <si>
-    <t>07.07.67</t>
-  </si>
-  <si>
-    <t>07.07.68</t>
-  </si>
-  <si>
-    <t>07.07.69</t>
-  </si>
-  <si>
-    <t>07.07.70</t>
-  </si>
-  <si>
-    <t>07.07.71</t>
-  </si>
-  <si>
-    <t>07.07.72</t>
-  </si>
-  <si>
-    <t>07.07.73</t>
-  </si>
-  <si>
-    <t>07.07.74</t>
-  </si>
-  <si>
-    <t>07.07.75</t>
-  </si>
-  <si>
-    <t>07.07.76</t>
-  </si>
-  <si>
-    <t>07.07.77</t>
-  </si>
-  <si>
-    <t>07.07.78</t>
-  </si>
-  <si>
-    <t>07.07.79</t>
-  </si>
-  <si>
-    <t>07.07.80</t>
-  </si>
-  <si>
-    <t>07.07.81</t>
-  </si>
-  <si>
-    <t>07.07.82</t>
-  </si>
-  <si>
-    <t>07.07.83</t>
-  </si>
-  <si>
-    <t>07.07.84</t>
-  </si>
-  <si>
-    <t>07.07.86</t>
-  </si>
-  <si>
-    <t>07.07.87</t>
-  </si>
-  <si>
-    <t>07.07.88</t>
-  </si>
-  <si>
-    <t>07.07.89</t>
-  </si>
-  <si>
-    <t>07.07.90</t>
-  </si>
-  <si>
-    <t>07.07.91</t>
-  </si>
-  <si>
-    <t>07.07.92</t>
-  </si>
-  <si>
-    <t>07.07.93</t>
-  </si>
-  <si>
-    <t>07.07.94</t>
-  </si>
-  <si>
-    <t>07.07.95</t>
-  </si>
-  <si>
-    <t>07.07.96</t>
-  </si>
-  <si>
-    <t>07.07.97</t>
-  </si>
-  <si>
-    <t>07.07.98</t>
-  </si>
-  <si>
-    <t>07.07.99</t>
-  </si>
-  <si>
-    <t>07.07.100</t>
-  </si>
-  <si>
-    <t>07.07.101</t>
-  </si>
-  <si>
-    <t>07.07.102</t>
-  </si>
-  <si>
-    <t>07.07.103</t>
-  </si>
-  <si>
-    <t>07.07.104</t>
-  </si>
-  <si>
-    <t>07.07.105</t>
-  </si>
-  <si>
-    <t>07.07.106</t>
-  </si>
-  <si>
-    <t>07.07.107</t>
-  </si>
-  <si>
-    <t>07.07.108</t>
-  </si>
-  <si>
-    <t>07.07.109</t>
-  </si>
-  <si>
-    <t>07.07.110</t>
-  </si>
-  <si>
-    <t>07.07.111</t>
-  </si>
-  <si>
-    <t>07.07.112</t>
-  </si>
-  <si>
-    <t>07.07.113</t>
-  </si>
-  <si>
-    <t>07.07.114</t>
-  </si>
-  <si>
-    <t>07.07.115</t>
-  </si>
-  <si>
-    <t>07.07.116</t>
-  </si>
-  <si>
-    <t>07.07.117</t>
-  </si>
-  <si>
-    <t>07.07.118</t>
-  </si>
-  <si>
-    <t>07.07.119</t>
-  </si>
-  <si>
-    <t>07.07.120</t>
-  </si>
-  <si>
-    <t>07.07.121</t>
-  </si>
-  <si>
-    <t>07.07.122</t>
-  </si>
-  <si>
-    <t>07.07.123</t>
-  </si>
-  <si>
-    <t>07.07.124</t>
-  </si>
-  <si>
-    <t>07.07.125</t>
-  </si>
-  <si>
-    <t>07.07.126</t>
-  </si>
-  <si>
-    <t>07.07.127</t>
-  </si>
-  <si>
-    <t>07.07.128</t>
-  </si>
-  <si>
-    <t>07.07.129</t>
-  </si>
-  <si>
-    <t>07.07.130</t>
-  </si>
-  <si>
-    <t>07.07.131</t>
-  </si>
-  <si>
-    <t>07.07.132</t>
-  </si>
-  <si>
-    <t>07.07.133</t>
-  </si>
-  <si>
-    <t>07.07.134</t>
-  </si>
-  <si>
-    <t>07.07.135</t>
-  </si>
-  <si>
-    <t>07.07.136</t>
-  </si>
-  <si>
-    <t>07.07.137</t>
-  </si>
-  <si>
-    <t>07.07.138</t>
-  </si>
-  <si>
-    <t>07.07.139</t>
-  </si>
-  <si>
-    <t>07.07.140</t>
-  </si>
-  <si>
-    <t>07.07.141</t>
-  </si>
-  <si>
-    <t>07.07.142</t>
-  </si>
-  <si>
-    <t>07.07.143</t>
-  </si>
-  <si>
-    <t>07.07.144</t>
-  </si>
-  <si>
-    <t>07.07.145</t>
-  </si>
-  <si>
-    <t>07.07.146</t>
-  </si>
-  <si>
-    <t>07.07.147</t>
-  </si>
-  <si>
-    <t>07.07.148</t>
-  </si>
-  <si>
-    <t>07.07.149</t>
-  </si>
-  <si>
-    <t>07.07.150</t>
-  </si>
-  <si>
-    <t>07.07.151</t>
-  </si>
-  <si>
-    <t>07.07.152</t>
+    <t>YT8880982299813</t>
+  </si>
+  <si>
+    <t>JT5498633122296</t>
+  </si>
+  <si>
+    <t>9817598337810</t>
+  </si>
+  <si>
+    <t>9817561906196</t>
+  </si>
+  <si>
+    <t>9817597042198</t>
+  </si>
+  <si>
+    <t>79116860524513</t>
+  </si>
+  <si>
+    <t>465453312175650</t>
+  </si>
+  <si>
+    <t>YT8881001428247</t>
+  </si>
+  <si>
+    <t>79117054093610</t>
+  </si>
+  <si>
+    <t>79116352158884</t>
+  </si>
+  <si>
+    <t>465455321353258</t>
+  </si>
+  <si>
+    <t>JT5499824273016</t>
+  </si>
+  <si>
+    <t>465448606440063</t>
+  </si>
+  <si>
+    <t>YT8881014957527</t>
+  </si>
+  <si>
+    <t>JT5499254571451</t>
+  </si>
+  <si>
+    <t>777420974852832</t>
+  </si>
+  <si>
+    <t>777421102032945</t>
+  </si>
+  <si>
+    <t>465453390178582</t>
+  </si>
+  <si>
+    <t>YT8881016845806</t>
+  </si>
+  <si>
+    <t>JT5499581951689</t>
+  </si>
+  <si>
+    <t>777422365205500</t>
+  </si>
+  <si>
+    <t>9817590201640</t>
+  </si>
+  <si>
+    <t>9817585314171</t>
+  </si>
+  <si>
+    <t>777422086167392</t>
+  </si>
+  <si>
+    <t>777422047937564</t>
+  </si>
+  <si>
+    <t>JT5499420492228</t>
+  </si>
+  <si>
+    <t>465456795812468</t>
+  </si>
+  <si>
+    <t>777421947371815</t>
+  </si>
+  <si>
+    <t>777422098989110</t>
+  </si>
+  <si>
+    <t>79117395794341</t>
+  </si>
+  <si>
+    <t>777422249209050</t>
+  </si>
+  <si>
+    <t>JT5499557335871</t>
+  </si>
+  <si>
+    <t>JT5499593076310</t>
+  </si>
+  <si>
+    <t>9817601310341</t>
+  </si>
+  <si>
+    <t>JT5499459270971</t>
+  </si>
+  <si>
+    <t>777421979396975</t>
+  </si>
+  <si>
+    <t>465451760956911</t>
+  </si>
+  <si>
+    <t>9817587706895</t>
+  </si>
+  <si>
+    <t>8258794480420</t>
+  </si>
+  <si>
+    <t>465454450241432</t>
+  </si>
+  <si>
+    <t>YT8881827269921</t>
+  </si>
+  <si>
+    <t>465457764900348</t>
+  </si>
+  <si>
+    <t>9817599918493</t>
+  </si>
+  <si>
+    <t>79117436311943</t>
+  </si>
+  <si>
+    <t>777422232180626</t>
+  </si>
+  <si>
+    <t>465459292330949</t>
+  </si>
+  <si>
+    <t>9817587676356</t>
+  </si>
+  <si>
+    <t>79117070893183</t>
+  </si>
+  <si>
+    <t>79014648854833</t>
+  </si>
+  <si>
+    <t>YT8881264556325</t>
+  </si>
+  <si>
+    <t>9817611933106</t>
+  </si>
+  <si>
+    <t>JT5499474471835</t>
+  </si>
+  <si>
+    <t>YT8881205713280</t>
+  </si>
+  <si>
+    <t>YT8881713805039</t>
+  </si>
+  <si>
+    <t>777422057138983</t>
+  </si>
+  <si>
+    <t>777422279578535</t>
+  </si>
+  <si>
+    <t>JT5499357097713</t>
+  </si>
+  <si>
+    <t>9817583571857</t>
+  </si>
+  <si>
+    <t>465459149313511</t>
+  </si>
+  <si>
+    <t>435243081637711</t>
+  </si>
+  <si>
+    <t>YT8881203079304</t>
+  </si>
+  <si>
+    <t>YT8881710489346</t>
+  </si>
+  <si>
+    <t>JT5499555318372</t>
+  </si>
+  <si>
+    <t>777422224291867</t>
+  </si>
+  <si>
+    <t>777421855554896</t>
+  </si>
+  <si>
+    <t>79117774445858</t>
+  </si>
+  <si>
+    <t>9817607428330</t>
+  </si>
+  <si>
+    <t>465450172258904</t>
+  </si>
+  <si>
+    <t>777421939569475</t>
+  </si>
+  <si>
+    <t>YT8881256136317</t>
+  </si>
+  <si>
+    <t>JT5499708160992</t>
+  </si>
+  <si>
+    <t>79117415228084</t>
+  </si>
+  <si>
+    <t>9817606613366</t>
+  </si>
+  <si>
+    <t>79117509710669</t>
+  </si>
+  <si>
+    <t>9817577879969</t>
+  </si>
+  <si>
+    <t>JT5499505166782</t>
+  </si>
+  <si>
+    <t>777421616975217</t>
+  </si>
+  <si>
+    <t>79117696250946</t>
+  </si>
+  <si>
+    <t>79117465527523</t>
+  </si>
+  <si>
+    <t>9817572476799</t>
+  </si>
+  <si>
+    <t>777422227310805</t>
+  </si>
+  <si>
+    <t>YT8881595284182</t>
+  </si>
+  <si>
+    <t>YT8882260952847</t>
+  </si>
+  <si>
+    <t>YT8882494776859</t>
+  </si>
+  <si>
+    <t>YT8881755208728</t>
+  </si>
+  <si>
+    <t>YT8881657240525</t>
+  </si>
+  <si>
+    <t>YT8882144681960</t>
+  </si>
+  <si>
+    <t>JT5500131975712</t>
+  </si>
+  <si>
+    <t>YT8881755210383</t>
+  </si>
+  <si>
+    <t>YT8881755208849</t>
+  </si>
+  <si>
+    <t>YT8882396047152</t>
+  </si>
+  <si>
+    <t>JT5499595952076</t>
+  </si>
+  <si>
+    <t>YT8882309071744</t>
+  </si>
+  <si>
+    <t>JT5500220106336</t>
+  </si>
+  <si>
+    <t>YT8882440004894</t>
+  </si>
+  <si>
+    <t>JT5499973731091</t>
+  </si>
+  <si>
+    <t>JT5500042212292</t>
+  </si>
+  <si>
+    <t>JT5500386588411</t>
+  </si>
+  <si>
+    <t>JT5500705303808</t>
+  </si>
+  <si>
+    <t>YT8881664761417</t>
+  </si>
+  <si>
+    <t>YT8882023690124</t>
+  </si>
+  <si>
+    <t>YT8881965706708</t>
+  </si>
+  <si>
+    <t>YT8882049235336</t>
+  </si>
+  <si>
+    <t>JT5500085421454</t>
+  </si>
+  <si>
+    <t>YT8881981266714</t>
+  </si>
+  <si>
+    <t>YT8882084279009</t>
+  </si>
+  <si>
+    <t>JT5500709369606</t>
+  </si>
+  <si>
+    <t>YT8882331018326</t>
+  </si>
+  <si>
+    <t>YT8881923064217</t>
+  </si>
+  <si>
+    <t>JT5500171686135</t>
+  </si>
+  <si>
+    <t>JT5500642188425</t>
+  </si>
+  <si>
+    <t>YT8882082598760</t>
+  </si>
+  <si>
+    <t>YT8882105763850</t>
+  </si>
+  <si>
+    <t>SF5112110102446</t>
+  </si>
+  <si>
+    <t>YT8881876085352</t>
+  </si>
+  <si>
+    <t>28.07.26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +538,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -574,7 +554,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -582,11 +562,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -597,9 +595,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -898,13 +903,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B127"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B302"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -912,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.6">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
@@ -920,1004 +925,2115 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.6">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6">
       <c r="A4" s="3">
         <v>79114287730818</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6">
       <c r="A5" s="3">
         <v>79113721261163</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6">
       <c r="A6" s="3">
         <v>79114199400506</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.6">
       <c r="A7" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.6">
       <c r="A8" s="3">
         <v>79114203887940</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.6">
       <c r="A9" s="3">
         <v>777418407164674</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.6">
       <c r="A10" s="3">
         <v>79114287731046</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.6">
       <c r="A11" s="3">
         <v>79114114585570</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.6">
       <c r="A12" s="3">
         <v>9817311547938</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.6">
       <c r="A13" s="3">
         <v>777418210107128</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.6">
       <c r="A14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.6">
       <c r="A15" s="3">
         <v>777418540098081</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.6">
       <c r="A16" s="3">
         <v>79114008929258</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.6">
       <c r="A17" s="3">
         <v>79114123496019</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.6">
       <c r="A18" s="3">
         <v>79011910916564</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.6">
       <c r="A19" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.6">
       <c r="A20" s="3">
         <v>79114056552890</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.6">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.6">
       <c r="A22" s="3">
         <v>79011810156917</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.6">
       <c r="A23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.6">
       <c r="A24" s="3">
         <v>79114129226699</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.6">
       <c r="A25" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.6">
       <c r="A26" s="3">
         <v>79114119950813</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.6">
       <c r="A27" s="3">
         <v>79113831226396</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.6">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.6">
       <c r="A29" s="3">
         <v>79114249344806</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.6">
       <c r="A30" s="3">
         <v>9817286636034</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.6">
       <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.6">
       <c r="A32" s="3">
         <v>9817306833974</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.6">
       <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.6">
       <c r="A34" s="3">
         <v>9817266811309</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.6">
       <c r="A35" s="3">
         <v>79114119952579</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.6">
       <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.6">
       <c r="A37" s="3">
         <v>79113859937536</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.6">
       <c r="A38" s="3">
         <v>9817310662063</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.6">
       <c r="A39" s="3">
         <v>79113826114819</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.6">
       <c r="A40" s="3">
         <v>79114123512156</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.6">
       <c r="A41" s="3">
         <v>9817293577073</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.6">
       <c r="A42" s="3">
         <v>79114123473093</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.6">
       <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.6">
       <c r="A44" s="3">
         <v>79114114546115</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.6">
       <c r="A45" s="3">
         <v>465426010024137</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.6">
       <c r="A46" s="3">
         <v>9817293845966</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.6">
       <c r="A47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.6">
       <c r="A48" s="3">
         <v>79114224672451</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.6">
       <c r="A49" s="3">
         <v>9817310661010</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.6">
       <c r="A50" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.6">
       <c r="A51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.6">
       <c r="A52" s="3">
         <v>79114096392960</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.6">
       <c r="A53" s="3">
         <v>777417680528740</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.6">
       <c r="A54" s="3">
         <v>79114114545731</v>
       </c>
       <c r="B54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.6">
       <c r="A55" s="3">
         <v>79114123470502</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.6">
       <c r="A56" s="3">
         <v>79114158480850</v>
       </c>
       <c r="B56" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.6">
       <c r="A57" s="3">
         <v>79114287730634</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.6">
       <c r="A58" s="3">
         <v>79011815866016</v>
       </c>
       <c r="B58" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.6">
       <c r="A59" s="3">
         <v>777418512271860</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.6">
       <c r="A60" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.6">
       <c r="A61" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.6">
       <c r="A62" s="3">
         <v>77419047733484</v>
       </c>
       <c r="B62" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.6">
       <c r="A63" s="3">
         <v>465430383814609</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.6">
       <c r="A64" s="3">
         <v>777419015424748</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.6">
       <c r="A65" s="3">
         <v>465429582994887</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.6">
       <c r="A66" s="3">
         <v>79114917851687</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.6">
       <c r="A67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.6">
       <c r="A68" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.6">
       <c r="A69" s="3">
         <v>79114362617905</v>
       </c>
       <c r="B69" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.6">
       <c r="A70" s="3">
         <v>79114362826221</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.6">
       <c r="A71" s="3">
         <v>79114362855049</v>
       </c>
       <c r="B71" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.6">
       <c r="A72" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.6">
       <c r="A73" s="3">
         <v>79114716195683</v>
       </c>
       <c r="B73" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.6">
       <c r="A74" s="3">
         <v>465432952519118</v>
       </c>
       <c r="B74" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.6">
       <c r="A75" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.6">
       <c r="A76" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.6">
       <c r="A77" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.6">
       <c r="A78" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.6">
       <c r="A79" s="3">
         <v>79114362617905</v>
       </c>
       <c r="B79" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.6">
       <c r="A80" s="3">
         <v>777419015424748</v>
       </c>
       <c r="B80" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.6">
       <c r="A81" s="3">
         <v>79114302102362</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="1">
         <v>79114218356055</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="1">
         <v>79012581856167</v>
       </c>
       <c r="B83" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="1">
         <v>79114409063138</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="1">
         <v>79114218396909</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="1">
         <v>9817337232960</v>
       </c>
       <c r="B86" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="1">
         <v>465426605460787</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B88" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="1">
         <v>79114347075820</v>
       </c>
       <c r="B89" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" s="1">
         <v>79114641590826</v>
       </c>
       <c r="B93" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B94" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B96" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
       <c r="A97" s="1">
         <v>777419080528783</v>
       </c>
       <c r="B97" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
       <c r="A99" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B99" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
       <c r="A100" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
       <c r="A101" s="1">
         <v>9817298550257</v>
       </c>
       <c r="B101" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
       <c r="A102" s="1">
         <v>9817338834087</v>
       </c>
       <c r="B102" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
       <c r="A103" s="1">
         <v>79114351420184</v>
       </c>
       <c r="B103" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
       <c r="A104" s="1">
         <v>79114523941757</v>
       </c>
       <c r="B104" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
       <c r="A106" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
       <c r="A107" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
       <c r="A109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B109" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
       <c r="A110" s="1">
         <v>465425273153619</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
       <c r="A111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
       <c r="A112" s="1">
         <v>79114272667800</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
       <c r="A113" s="1">
         <v>79114445687079</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
       <c r="A114" s="1">
         <v>777419340694859</v>
       </c>
       <c r="B114" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116" s="1">
         <v>777419197107227</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
       <c r="A117" s="1">
         <v>777419193134582</v>
       </c>
       <c r="B117" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118" s="1">
         <v>777419149591288</v>
       </c>
       <c r="B118" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
       <c r="A119" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
       <c r="A120" s="1">
         <v>465427544369324</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
       <c r="A121" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B122" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
       <c r="A123" s="1">
         <v>435227038851000</v>
       </c>
       <c r="B123" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B125" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
       <c r="A126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
       <c r="A127" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>175</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B129" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B130" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B131" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B132" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B133" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B134" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B135" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B136" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B137" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B139" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B140" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B141" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B142" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B143" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B144" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B145" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B146" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B147" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B148" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B149" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B150" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B151" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B152" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B153" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B154" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B155" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B156" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B157" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B158" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B159" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B160" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B161" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B162" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B163" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B164" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B165" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B166" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B168" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B169" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B170" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B171" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B172" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B173" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B174" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B175" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B176" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B177" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B178" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B179" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B180" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B181" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B182" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B183" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B184" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B185" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B186" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B187" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B188" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B189" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B190" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B191" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B192" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B193" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B194" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B195" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B196" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B197" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B198" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B199" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B200" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B201" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B202" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B203" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B204" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B205" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B206" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B207" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B208" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B209" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="15.6">
+      <c r="A210" s="3"/>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="1">
+        <v>777421971309997</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="1">
+        <v>79117952924235</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="1">
+        <v>465458300612210</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="1">
+        <v>465462997566968</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="1">
+        <v>9817637752976</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="1">
+        <v>777422386231741</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="1">
+        <v>777422549883964</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="1">
+        <v>777422741197359</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="1">
+        <v>79117641603383</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="1">
+        <v>777422423684474</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="1">
+        <v>79117947325687</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="1">
+        <v>777422657466151</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="1">
+        <v>79118115286962</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="1">
+        <v>465458348367580</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="1">
+        <v>465464907314970</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="1">
+        <v>777422134424763</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="1">
+        <v>9817706152080</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="1">
+        <v>9817641420345</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="1">
+        <v>9817618218214</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="1">
+        <v>777422513725104</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="1">
+        <v>79118024749653</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="1">
+        <v>777422657905926</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="1">
+        <v>777423203000463</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="1">
+        <v>777422413035587</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="1">
+        <v>79117818077517</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="1">
+        <v>777422517419094</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="1">
+        <v>9817699670146</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="1">
+        <v>9817626176674</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="1">
+        <v>465464033007149</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="1">
+        <v>9817684175880</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="1">
+        <v>9817638532752</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="1">
+        <v>79117975994426</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="1">
+        <v>777422279037036</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="1">
+        <v>465460191668107</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="1">
+        <v>465458538755029</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="1">
+        <v>9817633727498</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="1">
+        <v>79118367685893</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="1">
+        <v>9817700621226</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="1">
+        <v>79117796071346</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="1">
+        <v>465457962486311</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="1">
+        <v>777422731528745</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="1">
+        <v>465462045052132</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="1">
+        <v>777422556482984</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="1">
+        <v>465464224986141</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="1">
+        <v>465461539296139</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="1">
+        <v>777422770801355</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" s="1">
+        <v>777423239248503</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" s="1">
+        <v>79117651536910</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" s="1">
+        <v>79117933681198</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" s="1">
+        <v>9817627085660</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" s="1">
+        <v>777422282995768</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" s="1">
+        <v>777423239698605</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" s="1">
+        <v>465465103750961</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" s="1">
+        <v>9817620085910</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" s="1">
+        <v>465457413048475</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" s="1">
+        <v>465456211470405</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" s="1">
+        <v>465464532957747</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" s="1">
+        <v>777423140486346</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -1928,7 +3044,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1937,7 +3053,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/delivered.xlsx
+++ b/delivered.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="318">
   <si>
     <t>Date</t>
   </si>
@@ -517,6 +517,459 @@
   </si>
   <si>
     <t>28.07.26</t>
+  </si>
+  <si>
+    <t>79118824420191</t>
+  </si>
+  <si>
+    <t>465472981439634</t>
+  </si>
+  <si>
+    <t>JT5501371556169</t>
+  </si>
+  <si>
+    <t>777423766456070</t>
+  </si>
+  <si>
+    <t>777423791434285</t>
+  </si>
+  <si>
+    <t>465460557466698</t>
+  </si>
+  <si>
+    <t>YT8883049444988</t>
+  </si>
+  <si>
+    <t>79119115957783</t>
+  </si>
+  <si>
+    <t>465475730266001</t>
+  </si>
+  <si>
+    <t>79118908516350</t>
+  </si>
+  <si>
+    <t>YT8883182286722</t>
+  </si>
+  <si>
+    <t>79119040950183</t>
+  </si>
+  <si>
+    <t>79119327158321</t>
+  </si>
+  <si>
+    <t>9817718946799</t>
+  </si>
+  <si>
+    <t>79119089277103</t>
+  </si>
+  <si>
+    <t>9817751874305</t>
+  </si>
+  <si>
+    <t>79119471430708</t>
+  </si>
+  <si>
+    <t>79119050833173</t>
+  </si>
+  <si>
+    <t>YT8883723028714</t>
+  </si>
+  <si>
+    <t>9817605081138</t>
+  </si>
+  <si>
+    <t>9817784576370</t>
+  </si>
+  <si>
+    <t>YT8883849849679</t>
+  </si>
+  <si>
+    <t>9817753460786</t>
+  </si>
+  <si>
+    <t>9817769911867</t>
+  </si>
+  <si>
+    <t>JT5501535601748</t>
+  </si>
+  <si>
+    <t>YT8882874480068</t>
+  </si>
+  <si>
+    <t>79118833080186</t>
+  </si>
+  <si>
+    <t>79118979425089</t>
+  </si>
+  <si>
+    <t>JT5502597241614</t>
+  </si>
+  <si>
+    <t>777424572515165</t>
+  </si>
+  <si>
+    <t>9817653521677</t>
+  </si>
+  <si>
+    <t>777424114810896</t>
+  </si>
+  <si>
+    <t>79119137632359</t>
+  </si>
+  <si>
+    <t>JT5501299359983</t>
+  </si>
+  <si>
+    <t>465475448112441</t>
+  </si>
+  <si>
+    <t>YT8883626255907</t>
+  </si>
+  <si>
+    <t>9817780091264</t>
+  </si>
+  <si>
+    <t>79119299656526</t>
+  </si>
+  <si>
+    <t>YT8883742931987</t>
+  </si>
+  <si>
+    <t>777424092833669</t>
+  </si>
+  <si>
+    <t>777423532876975</t>
+  </si>
+  <si>
+    <t>465473412612728</t>
+  </si>
+  <si>
+    <t>777423875081346</t>
+  </si>
+  <si>
+    <t>777424007430464</t>
+  </si>
+  <si>
+    <t>YT8882892016005</t>
+  </si>
+  <si>
+    <t>777423571387306</t>
+  </si>
+  <si>
+    <t>9817736381529</t>
+  </si>
+  <si>
+    <t>JT5501077523127</t>
+  </si>
+  <si>
+    <t>YT8882970307102</t>
+  </si>
+  <si>
+    <t>777424099932425</t>
+  </si>
+  <si>
+    <t>777422837209675</t>
+  </si>
+  <si>
+    <t>JT5501302513659</t>
+  </si>
+  <si>
+    <t>YT8883239639732</t>
+  </si>
+  <si>
+    <t>465472312616126</t>
+  </si>
+  <si>
+    <t>YT8882580605650</t>
+  </si>
+  <si>
+    <t>465471732331470</t>
+  </si>
+  <si>
+    <t>YT8883674598074</t>
+  </si>
+  <si>
+    <t>465472002832188</t>
+  </si>
+  <si>
+    <t>777423767375582</t>
+  </si>
+  <si>
+    <t>777423745466795</t>
+  </si>
+  <si>
+    <t>JT5501532535801</t>
+  </si>
+  <si>
+    <t>777422996731755</t>
+  </si>
+  <si>
+    <t>465472391693106</t>
+  </si>
+  <si>
+    <t>777423677128532</t>
+  </si>
+  <si>
+    <t>JT5501532764591</t>
+  </si>
+  <si>
+    <t>JT5501372942277</t>
+  </si>
+  <si>
+    <t>777423009363641</t>
+  </si>
+  <si>
+    <t>777423648422955</t>
+  </si>
+  <si>
+    <t>79119161828030</t>
+  </si>
+  <si>
+    <t>79119122374228</t>
+  </si>
+  <si>
+    <t>9817726965432</t>
+  </si>
+  <si>
+    <t>YT8883410575516</t>
+  </si>
+  <si>
+    <t>79118705036709</t>
+  </si>
+  <si>
+    <t>777423955269542</t>
+  </si>
+  <si>
+    <t>465475481375138</t>
+  </si>
+  <si>
+    <t>YT8883595470376</t>
+  </si>
+  <si>
+    <t>79118257588609</t>
+  </si>
+  <si>
+    <t>YT888971825187</t>
+  </si>
+  <si>
+    <t>ＪＤＡＰ０３13258422</t>
+  </si>
+  <si>
+    <t>JDAP0313258422</t>
+  </si>
+  <si>
+    <t>79118367875866</t>
+  </si>
+  <si>
+    <t>777420282036519</t>
+  </si>
+  <si>
+    <t>79118276902896</t>
+  </si>
+  <si>
+    <t>79015519961480</t>
+  </si>
+  <si>
+    <t>79118373286841</t>
+  </si>
+  <si>
+    <t>JT550099745629</t>
+  </si>
+  <si>
+    <t>465474899950488</t>
+  </si>
+  <si>
+    <t>777422956038345</t>
+  </si>
+  <si>
+    <t>9817751764072</t>
+  </si>
+  <si>
+    <t>79118817209091</t>
+  </si>
+  <si>
+    <t>JT550478769131</t>
+  </si>
+  <si>
+    <t>79118138983288</t>
+  </si>
+  <si>
+    <t>ＹＴ８８８812345532</t>
+  </si>
+  <si>
+    <t>YT888812345532</t>
+  </si>
+  <si>
+    <t>79118656662606</t>
+  </si>
+  <si>
+    <t>777423388035728</t>
+  </si>
+  <si>
+    <t>ＹＴ８８８579129738</t>
+  </si>
+  <si>
+    <t>YT888579129738</t>
+  </si>
+  <si>
+    <t>9817758621431</t>
+  </si>
+  <si>
+    <t>YT8883068430782</t>
+  </si>
+  <si>
+    <t>YT888728725446</t>
+  </si>
+  <si>
+    <t>YT8882728725446</t>
+  </si>
+  <si>
+    <t>JT5500919745629</t>
+  </si>
+  <si>
+    <t>79015421313659</t>
+  </si>
+  <si>
+    <t>YT8883016778119</t>
+  </si>
+  <si>
+    <t>777422811535476</t>
+  </si>
+  <si>
+    <t>9817676881239</t>
+  </si>
+  <si>
+    <t>79118554290183</t>
+  </si>
+  <si>
+    <t>777423080271777</t>
+  </si>
+  <si>
+    <t>777422831741276</t>
+  </si>
+  <si>
+    <t>79118644923859</t>
+  </si>
+  <si>
+    <t>79118717367067</t>
+  </si>
+  <si>
+    <t>9817659220150</t>
+  </si>
+  <si>
+    <t>777423193264153</t>
+  </si>
+  <si>
+    <t>79118615476461</t>
+  </si>
+  <si>
+    <t>777423262190233</t>
+  </si>
+  <si>
+    <t>465463953627717</t>
+  </si>
+  <si>
+    <t>79118522980734</t>
+  </si>
+  <si>
+    <t>79118579258190</t>
+  </si>
+  <si>
+    <t>465459643712698</t>
+  </si>
+  <si>
+    <t>465466976923906</t>
+  </si>
+  <si>
+    <t>9817751470985</t>
+  </si>
+  <si>
+    <t>JT3168752156470</t>
+  </si>
+  <si>
+    <t>YT8881866116899</t>
+  </si>
+  <si>
+    <t>79118432746656</t>
+  </si>
+  <si>
+    <t>465468421375906</t>
+  </si>
+  <si>
+    <t>YT8883165794725</t>
+  </si>
+  <si>
+    <t>465467345765080</t>
+  </si>
+  <si>
+    <t>JT5500938255508</t>
+  </si>
+  <si>
+    <t>JT5500670686464</t>
+  </si>
+  <si>
+    <t>465475987318740</t>
+  </si>
+  <si>
+    <t>YT8881966666733</t>
+  </si>
+  <si>
+    <t>777422847337625</t>
+  </si>
+  <si>
+    <t>YT8882001189556</t>
+  </si>
+  <si>
+    <t>JT5500848779222</t>
+  </si>
+  <si>
+    <t>YT8882076042439</t>
+  </si>
+  <si>
+    <t>YT8881950927855</t>
+  </si>
+  <si>
+    <t>777423349497530</t>
+  </si>
+  <si>
+    <t>YT8882024475728</t>
+  </si>
+  <si>
+    <t>79118247028763</t>
+  </si>
+  <si>
+    <t>9817650895696</t>
+  </si>
+  <si>
+    <t>79118249168211</t>
+  </si>
+  <si>
+    <t>465466346707418</t>
+  </si>
+  <si>
+    <t>465467113069181</t>
+  </si>
+  <si>
+    <t>777423445904215</t>
+  </si>
+  <si>
+    <t>9817714904846</t>
+  </si>
+  <si>
+    <t>9817688850817</t>
+  </si>
+  <si>
+    <t>79118141365896</t>
+  </si>
+  <si>
+    <t>JT5501195769597</t>
+  </si>
+  <si>
+    <t>777423146909811</t>
+  </si>
+  <si>
+    <t>777423269005541</t>
   </si>
 </sst>
 </file>
@@ -903,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B458"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -3034,6 +3487,776 @@
     <row r="302" spans="1:1">
       <c r="A302" s="1" t="s">
         <v>165</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" s="5" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1">
+      <c r="A353" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1">
+      <c r="A354" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1">
+      <c r="A355" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1">
+      <c r="A356" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1">
+      <c r="A357" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1">
+      <c r="A358" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1">
+      <c r="A359" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1">
+      <c r="A360" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1">
+      <c r="A361" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1">
+      <c r="A362" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1">
+      <c r="A363" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1">
+      <c r="A364" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1">
+      <c r="A365" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1">
+      <c r="A366" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1">
+      <c r="A367" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1">
+      <c r="A368" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" s="5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1">
+      <c r="A438" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1">
+      <c r="A439" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1">
+      <c r="A440" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1">
+      <c r="A441" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1">
+      <c r="A442" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="5" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="5" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="5" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/delivered.xlsx
+++ b/delivered.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="572">
   <si>
     <t>Date</t>
   </si>
@@ -171,354 +171,6 @@
     <t>07.07.26</t>
   </si>
   <si>
-    <t>YT8880982299813</t>
-  </si>
-  <si>
-    <t>JT5498633122296</t>
-  </si>
-  <si>
-    <t>9817598337810</t>
-  </si>
-  <si>
-    <t>9817561906196</t>
-  </si>
-  <si>
-    <t>9817597042198</t>
-  </si>
-  <si>
-    <t>79116860524513</t>
-  </si>
-  <si>
-    <t>465453312175650</t>
-  </si>
-  <si>
-    <t>YT8881001428247</t>
-  </si>
-  <si>
-    <t>79117054093610</t>
-  </si>
-  <si>
-    <t>79116352158884</t>
-  </si>
-  <si>
-    <t>465455321353258</t>
-  </si>
-  <si>
-    <t>JT5499824273016</t>
-  </si>
-  <si>
-    <t>465448606440063</t>
-  </si>
-  <si>
-    <t>YT8881014957527</t>
-  </si>
-  <si>
-    <t>JT5499254571451</t>
-  </si>
-  <si>
-    <t>777420974852832</t>
-  </si>
-  <si>
-    <t>777421102032945</t>
-  </si>
-  <si>
-    <t>465453390178582</t>
-  </si>
-  <si>
-    <t>YT8881016845806</t>
-  </si>
-  <si>
-    <t>JT5499581951689</t>
-  </si>
-  <si>
-    <t>777422365205500</t>
-  </si>
-  <si>
-    <t>9817590201640</t>
-  </si>
-  <si>
-    <t>9817585314171</t>
-  </si>
-  <si>
-    <t>777422086167392</t>
-  </si>
-  <si>
-    <t>777422047937564</t>
-  </si>
-  <si>
-    <t>JT5499420492228</t>
-  </si>
-  <si>
-    <t>465456795812468</t>
-  </si>
-  <si>
-    <t>777421947371815</t>
-  </si>
-  <si>
-    <t>777422098989110</t>
-  </si>
-  <si>
-    <t>79117395794341</t>
-  </si>
-  <si>
-    <t>777422249209050</t>
-  </si>
-  <si>
-    <t>JT5499557335871</t>
-  </si>
-  <si>
-    <t>JT5499593076310</t>
-  </si>
-  <si>
-    <t>9817601310341</t>
-  </si>
-  <si>
-    <t>JT5499459270971</t>
-  </si>
-  <si>
-    <t>777421979396975</t>
-  </si>
-  <si>
-    <t>465451760956911</t>
-  </si>
-  <si>
-    <t>9817587706895</t>
-  </si>
-  <si>
-    <t>8258794480420</t>
-  </si>
-  <si>
-    <t>465454450241432</t>
-  </si>
-  <si>
-    <t>YT8881827269921</t>
-  </si>
-  <si>
-    <t>465457764900348</t>
-  </si>
-  <si>
-    <t>9817599918493</t>
-  </si>
-  <si>
-    <t>79117436311943</t>
-  </si>
-  <si>
-    <t>777422232180626</t>
-  </si>
-  <si>
-    <t>465459292330949</t>
-  </si>
-  <si>
-    <t>9817587676356</t>
-  </si>
-  <si>
-    <t>79117070893183</t>
-  </si>
-  <si>
-    <t>79014648854833</t>
-  </si>
-  <si>
-    <t>YT8881264556325</t>
-  </si>
-  <si>
-    <t>9817611933106</t>
-  </si>
-  <si>
-    <t>JT5499474471835</t>
-  </si>
-  <si>
-    <t>YT8881205713280</t>
-  </si>
-  <si>
-    <t>YT8881713805039</t>
-  </si>
-  <si>
-    <t>777422057138983</t>
-  </si>
-  <si>
-    <t>777422279578535</t>
-  </si>
-  <si>
-    <t>JT5499357097713</t>
-  </si>
-  <si>
-    <t>9817583571857</t>
-  </si>
-  <si>
-    <t>465459149313511</t>
-  </si>
-  <si>
-    <t>435243081637711</t>
-  </si>
-  <si>
-    <t>YT8881203079304</t>
-  </si>
-  <si>
-    <t>YT8881710489346</t>
-  </si>
-  <si>
-    <t>JT5499555318372</t>
-  </si>
-  <si>
-    <t>777422224291867</t>
-  </si>
-  <si>
-    <t>777421855554896</t>
-  </si>
-  <si>
-    <t>79117774445858</t>
-  </si>
-  <si>
-    <t>9817607428330</t>
-  </si>
-  <si>
-    <t>465450172258904</t>
-  </si>
-  <si>
-    <t>777421939569475</t>
-  </si>
-  <si>
-    <t>YT8881256136317</t>
-  </si>
-  <si>
-    <t>JT5499708160992</t>
-  </si>
-  <si>
-    <t>79117415228084</t>
-  </si>
-  <si>
-    <t>9817606613366</t>
-  </si>
-  <si>
-    <t>79117509710669</t>
-  </si>
-  <si>
-    <t>9817577879969</t>
-  </si>
-  <si>
-    <t>JT5499505166782</t>
-  </si>
-  <si>
-    <t>777421616975217</t>
-  </si>
-  <si>
-    <t>79117696250946</t>
-  </si>
-  <si>
-    <t>79117465527523</t>
-  </si>
-  <si>
-    <t>9817572476799</t>
-  </si>
-  <si>
-    <t>777422227310805</t>
-  </si>
-  <si>
-    <t>YT8881595284182</t>
-  </si>
-  <si>
-    <t>YT8882260952847</t>
-  </si>
-  <si>
-    <t>YT8882494776859</t>
-  </si>
-  <si>
-    <t>YT8881755208728</t>
-  </si>
-  <si>
-    <t>YT8881657240525</t>
-  </si>
-  <si>
-    <t>YT8882144681960</t>
-  </si>
-  <si>
-    <t>JT5500131975712</t>
-  </si>
-  <si>
-    <t>YT8881755210383</t>
-  </si>
-  <si>
-    <t>YT8881755208849</t>
-  </si>
-  <si>
-    <t>YT8882396047152</t>
-  </si>
-  <si>
-    <t>JT5499595952076</t>
-  </si>
-  <si>
-    <t>YT8882309071744</t>
-  </si>
-  <si>
-    <t>JT5500220106336</t>
-  </si>
-  <si>
-    <t>YT8882440004894</t>
-  </si>
-  <si>
-    <t>JT5499973731091</t>
-  </si>
-  <si>
-    <t>JT5500042212292</t>
-  </si>
-  <si>
-    <t>JT5500386588411</t>
-  </si>
-  <si>
-    <t>JT5500705303808</t>
-  </si>
-  <si>
-    <t>YT8881664761417</t>
-  </si>
-  <si>
-    <t>YT8882023690124</t>
-  </si>
-  <si>
-    <t>YT8881965706708</t>
-  </si>
-  <si>
-    <t>YT8882049235336</t>
-  </si>
-  <si>
-    <t>JT5500085421454</t>
-  </si>
-  <si>
-    <t>YT8881981266714</t>
-  </si>
-  <si>
-    <t>YT8882084279009</t>
-  </si>
-  <si>
-    <t>JT5500709369606</t>
-  </si>
-  <si>
-    <t>YT8882331018326</t>
-  </si>
-  <si>
-    <t>YT8881923064217</t>
-  </si>
-  <si>
-    <t>JT5500171686135</t>
-  </si>
-  <si>
-    <t>JT5500642188425</t>
-  </si>
-  <si>
-    <t>YT8882082598760</t>
-  </si>
-  <si>
-    <t>YT8882105763850</t>
-  </si>
-  <si>
-    <t>SF5112110102446</t>
-  </si>
-  <si>
-    <t>YT8881876085352</t>
-  </si>
-  <si>
-    <t>28.07.26</t>
-  </si>
-  <si>
     <t>79118824420191</t>
   </si>
   <si>
@@ -970,6 +622,1116 @@
   </si>
   <si>
     <t>777423269005541</t>
+  </si>
+  <si>
+    <t>YT8884755194668</t>
+  </si>
+  <si>
+    <t>79120571661088</t>
+  </si>
+  <si>
+    <t>73716426051276</t>
+  </si>
+  <si>
+    <t>777425552263142</t>
+  </si>
+  <si>
+    <t>773430169099707</t>
+  </si>
+  <si>
+    <t>777425497747169</t>
+  </si>
+  <si>
+    <t>79120492216951</t>
+  </si>
+  <si>
+    <t>JT5503909880771</t>
+  </si>
+  <si>
+    <t>777425406799771</t>
+  </si>
+  <si>
+    <t>YT8884929245680</t>
+  </si>
+  <si>
+    <t>JT5503756413585</t>
+  </si>
+  <si>
+    <t>79120273943032</t>
+  </si>
+  <si>
+    <t>777425512853696</t>
+  </si>
+  <si>
+    <t>465494472191076</t>
+  </si>
+  <si>
+    <t>465485363226456</t>
+  </si>
+  <si>
+    <t>465486045639866</t>
+  </si>
+  <si>
+    <t>YT8884901508329</t>
+  </si>
+  <si>
+    <t>465485289856256</t>
+  </si>
+  <si>
+    <t>465485672986262</t>
+  </si>
+  <si>
+    <t>YT8884756076626</t>
+  </si>
+  <si>
+    <t>777425538961039</t>
+  </si>
+  <si>
+    <t>777425492400505</t>
+  </si>
+  <si>
+    <t>777425376893025</t>
+  </si>
+  <si>
+    <t>YT8885713972711</t>
+  </si>
+  <si>
+    <t>465493047946239</t>
+  </si>
+  <si>
+    <t>YT8884852002725</t>
+  </si>
+  <si>
+    <t>JT5503934267516</t>
+  </si>
+  <si>
+    <t>JT5503723040860</t>
+  </si>
+  <si>
+    <t>777425217523315</t>
+  </si>
+  <si>
+    <t>YT8884777619042</t>
+  </si>
+  <si>
+    <t>JT5503980623746</t>
+  </si>
+  <si>
+    <t>YT8885213220312</t>
+  </si>
+  <si>
+    <t>777425614036297</t>
+  </si>
+  <si>
+    <t>YT8884804050635</t>
+  </si>
+  <si>
+    <t>JT9001470362258</t>
+  </si>
+  <si>
+    <t>465484039936407</t>
+  </si>
+  <si>
+    <t>JT5503943390671</t>
+  </si>
+  <si>
+    <t>YT8884779828624</t>
+  </si>
+  <si>
+    <t>79120994662956</t>
+  </si>
+  <si>
+    <t>9817903095048</t>
+  </si>
+  <si>
+    <t>79120926941206</t>
+  </si>
+  <si>
+    <t>YT7631927398745</t>
+  </si>
+  <si>
+    <t>JT5503946278929</t>
+  </si>
+  <si>
+    <t>YT8884674366823</t>
+  </si>
+  <si>
+    <t>465484052406977</t>
+  </si>
+  <si>
+    <t>777425075185916</t>
+  </si>
+  <si>
+    <t>777424952193652</t>
+  </si>
+  <si>
+    <t>YT8884549928833</t>
+  </si>
+  <si>
+    <t>777425532295679</t>
+  </si>
+  <si>
+    <t>777425292337950</t>
+  </si>
+  <si>
+    <t>777425561922513</t>
+  </si>
+  <si>
+    <t>465483864393112</t>
+  </si>
+  <si>
+    <t>79121420106957</t>
+  </si>
+  <si>
+    <t>9817900423455</t>
+  </si>
+  <si>
+    <t>JT5503614888010</t>
+  </si>
+  <si>
+    <t>JDAP03199174222</t>
+  </si>
+  <si>
+    <t>9817858283449</t>
+  </si>
+  <si>
+    <t>YT8884867106797</t>
+  </si>
+  <si>
+    <t>777425029418984</t>
+  </si>
+  <si>
+    <t>777424939805614</t>
+  </si>
+  <si>
+    <t>79120583583816</t>
+  </si>
+  <si>
+    <t>777425556295308</t>
+  </si>
+  <si>
+    <t>YT7631737508840</t>
+  </si>
+  <si>
+    <t>YT8884855694613</t>
+  </si>
+  <si>
+    <t>JT5503622166402</t>
+  </si>
+  <si>
+    <t>79121035460932</t>
+  </si>
+  <si>
+    <t>YT8884665198192</t>
+  </si>
+  <si>
+    <t>79120737015066</t>
+  </si>
+  <si>
+    <t>773430615417672</t>
+  </si>
+  <si>
+    <t>9817911190682</t>
+  </si>
+  <si>
+    <t>YT8885608190598</t>
+  </si>
+  <si>
+    <t>YT8884560989732</t>
+  </si>
+  <si>
+    <t>JT5503598011345</t>
+  </si>
+  <si>
+    <t>465493030554901</t>
+  </si>
+  <si>
+    <t>JT5503312311887</t>
+  </si>
+  <si>
+    <t>JT5503788424481</t>
+  </si>
+  <si>
+    <t>773430619143253</t>
+  </si>
+  <si>
+    <t>465483610812509</t>
+  </si>
+  <si>
+    <t>777424986197449</t>
+  </si>
+  <si>
+    <t>YT8884843406758</t>
+  </si>
+  <si>
+    <t>465485939540824</t>
+  </si>
+  <si>
+    <t>777425442675982</t>
+  </si>
+  <si>
+    <t>777425354589800</t>
+  </si>
+  <si>
+    <t>777425328442133</t>
+  </si>
+  <si>
+    <t>JT5503665519773</t>
+  </si>
+  <si>
+    <t>JT5503356984126</t>
+  </si>
+  <si>
+    <t>777424952568763</t>
+  </si>
+  <si>
+    <t>YT8884280552889</t>
+  </si>
+  <si>
+    <t>79121004489806</t>
+  </si>
+  <si>
+    <t>465484249602894</t>
+  </si>
+  <si>
+    <t>465493029458794</t>
+  </si>
+  <si>
+    <t>9817904648526</t>
+  </si>
+  <si>
+    <t>465486424671792</t>
+  </si>
+  <si>
+    <t>79120513891281</t>
+  </si>
+  <si>
+    <t>777425078148667</t>
+  </si>
+  <si>
+    <t>JT5503731539655</t>
+  </si>
+  <si>
+    <t>773430488632225</t>
+  </si>
+  <si>
+    <t>9817883876957</t>
+  </si>
+  <si>
+    <t>79120771222043</t>
+  </si>
+  <si>
+    <t>465494207464740</t>
+  </si>
+  <si>
+    <t>79120859994050</t>
+  </si>
+  <si>
+    <t>9817857282681</t>
+  </si>
+  <si>
+    <t>YT2544888435581</t>
+  </si>
+  <si>
+    <t>465494671170125</t>
+  </si>
+  <si>
+    <t>777425635070207</t>
+  </si>
+  <si>
+    <t>9817917146012</t>
+  </si>
+  <si>
+    <t>777425437843233</t>
+  </si>
+  <si>
+    <t>465495973466450</t>
+  </si>
+  <si>
+    <t>9817914931482</t>
+  </si>
+  <si>
+    <t>YT8885720429350</t>
+  </si>
+  <si>
+    <t>79121247992132</t>
+  </si>
+  <si>
+    <t>9817855386753</t>
+  </si>
+  <si>
+    <t>79120808394858</t>
+  </si>
+  <si>
+    <t>9817907816815</t>
+  </si>
+  <si>
+    <t>9817914022790</t>
+  </si>
+  <si>
+    <t>79120925438667</t>
+  </si>
+  <si>
+    <t>9817886341964</t>
+  </si>
+  <si>
+    <t>777425644089342</t>
+  </si>
+  <si>
+    <t>465483971196465</t>
+  </si>
+  <si>
+    <t>9817917440595</t>
+  </si>
+  <si>
+    <t>05.07.2026</t>
+  </si>
+  <si>
+    <t>08.07.2026</t>
+  </si>
+  <si>
+    <t>777424220162412</t>
+  </si>
+  <si>
+    <t>465478890570558</t>
+  </si>
+  <si>
+    <t>465478836046637</t>
+  </si>
+  <si>
+    <t>YT8883903450609</t>
+  </si>
+  <si>
+    <t>JT5502579705752</t>
+  </si>
+  <si>
+    <t>777424450392984</t>
+  </si>
+  <si>
+    <t>777423915519907</t>
+  </si>
+  <si>
+    <t>YT8883891190132</t>
+  </si>
+  <si>
+    <t>79119334943698</t>
+  </si>
+  <si>
+    <t>465478695635802</t>
+  </si>
+  <si>
+    <t>777424019456798</t>
+  </si>
+  <si>
+    <t>465476542484994</t>
+  </si>
+  <si>
+    <t>465469564298701</t>
+  </si>
+  <si>
+    <t>JT5502224005826</t>
+  </si>
+  <si>
+    <t>JT5502578278301</t>
+  </si>
+  <si>
+    <t>JT5502396965926</t>
+  </si>
+  <si>
+    <t>YT8884489615042</t>
+  </si>
+  <si>
+    <t>JT5502242836349</t>
+  </si>
+  <si>
+    <t>YT8883878440548</t>
+  </si>
+  <si>
+    <t>777423993882325</t>
+  </si>
+  <si>
+    <t>777424713674098</t>
+  </si>
+  <si>
+    <t>JT5502298396291</t>
+  </si>
+  <si>
+    <t>YT8884117072986</t>
+  </si>
+  <si>
+    <t>JT5502070896573</t>
+  </si>
+  <si>
+    <t>465471994471730</t>
+  </si>
+  <si>
+    <t>777424752557155</t>
+  </si>
+  <si>
+    <t>JT5502515695069</t>
+  </si>
+  <si>
+    <t>777423826557941</t>
+  </si>
+  <si>
+    <t>465480645383240</t>
+  </si>
+  <si>
+    <t>JT5503266812933</t>
+  </si>
+  <si>
+    <t>79120332036445</t>
+  </si>
+  <si>
+    <t>465473534442564</t>
+  </si>
+  <si>
+    <t>465470049614367</t>
+  </si>
+  <si>
+    <t>YT8883878678840</t>
+  </si>
+  <si>
+    <t>JT5502695633268</t>
+  </si>
+  <si>
+    <t>79120061027112</t>
+  </si>
+  <si>
+    <t>YT8884336503775</t>
+  </si>
+  <si>
+    <t>79119935578123</t>
+  </si>
+  <si>
+    <t>79119902597646</t>
+  </si>
+  <si>
+    <t>9817844495105</t>
+  </si>
+  <si>
+    <t>79119333092366</t>
+  </si>
+  <si>
+    <t>465481632912782</t>
+  </si>
+  <si>
+    <t>777424342650506</t>
+  </si>
+  <si>
+    <t>JT5502741718081</t>
+  </si>
+  <si>
+    <t>79119623086735</t>
+  </si>
+  <si>
+    <t>JT5502253986072</t>
+  </si>
+  <si>
+    <t>JT5502750696507</t>
+  </si>
+  <si>
+    <t>79119364223825</t>
+  </si>
+  <si>
+    <t>YT8883932774068</t>
+  </si>
+  <si>
+    <t>9817833727780</t>
+  </si>
+  <si>
+    <t>79119682173315</t>
+  </si>
+  <si>
+    <t>465478907911956</t>
+  </si>
+  <si>
+    <t>79016454897614</t>
+  </si>
+  <si>
+    <t>79119373863903</t>
+  </si>
+  <si>
+    <t>79119699371877</t>
+  </si>
+  <si>
+    <t>9817814907148</t>
+  </si>
+  <si>
+    <t>79120384923273</t>
+  </si>
+  <si>
+    <t>777424230198347</t>
+  </si>
+  <si>
+    <t>9817817261348</t>
+  </si>
+  <si>
+    <t>JT5502063985498</t>
+  </si>
+  <si>
+    <t>79119416390403</t>
+  </si>
+  <si>
+    <t>79120038283526</t>
+  </si>
+  <si>
+    <t>79119353172438</t>
+  </si>
+  <si>
+    <t>9817817233388</t>
+  </si>
+  <si>
+    <t>JT9001357075546</t>
+  </si>
+  <si>
+    <t>9817802550951</t>
+  </si>
+  <si>
+    <t>YT8884389671506</t>
+  </si>
+  <si>
+    <t>JT5502803401712</t>
+  </si>
+  <si>
+    <t>465480494417993</t>
+  </si>
+  <si>
+    <t>YT8883889378511</t>
+  </si>
+  <si>
+    <t>JT5501949529727</t>
+  </si>
+  <si>
+    <t>9817783262947</t>
+  </si>
+  <si>
+    <t>777424563328445</t>
+  </si>
+  <si>
+    <t>JT5502586459458</t>
+  </si>
+  <si>
+    <t>JT5502038877683</t>
+  </si>
+  <si>
+    <t>777424953542826</t>
+  </si>
+  <si>
+    <t>79119680373126</t>
+  </si>
+  <si>
+    <t>9817833357257</t>
+  </si>
+  <si>
+    <t>9817744360683</t>
+  </si>
+  <si>
+    <t>9817824222503</t>
+  </si>
+  <si>
+    <t>9817842086178</t>
+  </si>
+  <si>
+    <t>YT8884426509513</t>
+  </si>
+  <si>
+    <t>465478784045939</t>
+  </si>
+  <si>
+    <t>79120061484942</t>
+  </si>
+  <si>
+    <t>79016630818351</t>
+  </si>
+  <si>
+    <t>777424241079598</t>
+  </si>
+  <si>
+    <t>465482477918590</t>
+  </si>
+  <si>
+    <t>YT8884120626190</t>
+  </si>
+  <si>
+    <t>YT8884258229922</t>
+  </si>
+  <si>
+    <t>JT3169425015783</t>
+  </si>
+  <si>
+    <t>777424168124852</t>
+  </si>
+  <si>
+    <t>9817726240838</t>
+  </si>
+  <si>
+    <t>79120328238119</t>
+  </si>
+  <si>
+    <t>79120018634046</t>
+  </si>
+  <si>
+    <t>JT5502797492566</t>
+  </si>
+  <si>
+    <t>YT8883447163830</t>
+  </si>
+  <si>
+    <t>79119513045156</t>
+  </si>
+  <si>
+    <t>777424993812033</t>
+  </si>
+  <si>
+    <t>465476500993347</t>
+  </si>
+  <si>
+    <t>777424361174079</t>
+  </si>
+  <si>
+    <t>9817874570506</t>
+  </si>
+  <si>
+    <t>465479229384518</t>
+  </si>
+  <si>
+    <t>12.07.2026</t>
+  </si>
+  <si>
+    <t>14.07.2026</t>
+  </si>
+  <si>
+    <t>YT7632675835236</t>
+  </si>
+  <si>
+    <t>9817955045050</t>
+  </si>
+  <si>
+    <t>9817966082788</t>
+  </si>
+  <si>
+    <t>YT8885905743570</t>
+  </si>
+  <si>
+    <t>777426806685057</t>
+  </si>
+  <si>
+    <t>79121799191425</t>
+  </si>
+  <si>
+    <t>9817971903882</t>
+  </si>
+  <si>
+    <t>79121608498840</t>
+  </si>
+  <si>
+    <t>79121527527448</t>
+  </si>
+  <si>
+    <t>465501494935518</t>
+  </si>
+  <si>
+    <t>9817956925032</t>
+  </si>
+  <si>
+    <t>9817958820639</t>
+  </si>
+  <si>
+    <t>JT5505201778852</t>
+  </si>
+  <si>
+    <t>79121981513759</t>
+  </si>
+  <si>
+    <t>79121727019157</t>
+  </si>
+  <si>
+    <t>9817966084147</t>
+  </si>
+  <si>
+    <t>9817943793166</t>
+  </si>
+  <si>
+    <t>9817954030235</t>
+  </si>
+  <si>
+    <t>YT8886196738528</t>
+  </si>
+  <si>
+    <t>79121667178404</t>
+  </si>
+  <si>
+    <t>YT8885969781930</t>
+  </si>
+  <si>
+    <t>777426778488134</t>
+  </si>
+  <si>
+    <t>9817951581468</t>
+  </si>
+  <si>
+    <t>465502104232434</t>
+  </si>
+  <si>
+    <t>777426457494875</t>
+  </si>
+  <si>
+    <t>465500678686356</t>
+  </si>
+  <si>
+    <t>JT5505282889514</t>
+  </si>
+  <si>
+    <t>79121800010852</t>
+  </si>
+  <si>
+    <t>777426502141976</t>
+  </si>
+  <si>
+    <t>79121636735126</t>
+  </si>
+  <si>
+    <t>465501199601972</t>
+  </si>
+  <si>
+    <t>JT5504998948258</t>
+  </si>
+  <si>
+    <t>9817949573418</t>
+  </si>
+  <si>
+    <t>79121618345607</t>
+  </si>
+  <si>
+    <t>JT5504825809292</t>
+  </si>
+  <si>
+    <t>JT5505255975481</t>
+  </si>
+  <si>
+    <t>_x000D_17.07.2026</t>
+  </si>
+  <si>
+    <t>79122498404692</t>
+  </si>
+  <si>
+    <t>79122824512889</t>
+  </si>
+  <si>
+    <t>JT5504942213349</t>
+  </si>
+  <si>
+    <t>465503689108873</t>
+  </si>
+  <si>
+    <t>YT8886384406516</t>
+  </si>
+  <si>
+    <t>777426672106640</t>
+  </si>
+  <si>
+    <t>465508194640408</t>
+  </si>
+  <si>
+    <t>YT8886672643157</t>
+  </si>
+  <si>
+    <t>YT8886765884971</t>
+  </si>
+  <si>
+    <t>79122239505024</t>
+  </si>
+  <si>
+    <t>465502154312880</t>
+  </si>
+  <si>
+    <t>79122531626386</t>
+  </si>
+  <si>
+    <t>JT5505439599036</t>
+  </si>
+  <si>
+    <t>777427346837197</t>
+  </si>
+  <si>
+    <t>465509376161976</t>
+  </si>
+  <si>
+    <t>JT5506545455404</t>
+  </si>
+  <si>
+    <t>9818062333520</t>
+  </si>
+  <si>
+    <t>YT8885952562674</t>
+  </si>
+  <si>
+    <t>777427087637042</t>
+  </si>
+  <si>
+    <t>465509754781473</t>
+  </si>
+  <si>
+    <t>79122940553887</t>
+  </si>
+  <si>
+    <t>79122143971445</t>
+  </si>
+  <si>
+    <t>777426587500268</t>
+  </si>
+  <si>
+    <t>YT8886581615609</t>
+  </si>
+  <si>
+    <t>79122539705596</t>
+  </si>
+  <si>
+    <t>JT5504307209131</t>
+  </si>
+  <si>
+    <t>JT5504307726856</t>
+  </si>
+  <si>
+    <t>465500863123295</t>
+  </si>
+  <si>
+    <t>9817997645724</t>
+  </si>
+  <si>
+    <t>777427358319738</t>
+  </si>
+  <si>
+    <t>JT5505709983398</t>
+  </si>
+  <si>
+    <t>JT5505149288184</t>
+  </si>
+  <si>
+    <t>465507254476899</t>
+  </si>
+  <si>
+    <t>465508782347677</t>
+  </si>
+  <si>
+    <t>JT5505589725403</t>
+  </si>
+  <si>
+    <t>79122258818446</t>
+  </si>
+  <si>
+    <t>YT8885333846328</t>
+  </si>
+  <si>
+    <t>YT7632094972824</t>
+  </si>
+  <si>
+    <t>YT7633058282366</t>
+  </si>
+  <si>
+    <t>465492724651609</t>
+  </si>
+  <si>
+    <t>YT7632865500214</t>
+  </si>
+  <si>
+    <t>73717328976746</t>
+  </si>
+  <si>
+    <t>79122191195930</t>
+  </si>
+  <si>
+    <t>JT5505896621144</t>
+  </si>
+  <si>
+    <t>YT8887180283699</t>
+  </si>
+  <si>
+    <t>YT8886635357071</t>
+  </si>
+  <si>
+    <t>465506921261332</t>
+  </si>
+  <si>
+    <t>9818049060949</t>
+  </si>
+  <si>
+    <t>777426896912398</t>
+  </si>
+  <si>
+    <t>YT8886915531472</t>
+  </si>
+  <si>
+    <t>JT5505595034152</t>
+  </si>
+  <si>
+    <t>465506506662766</t>
+  </si>
+  <si>
+    <t>JT5505661002107</t>
+  </si>
+  <si>
+    <t>79122909191923</t>
+  </si>
+  <si>
+    <t>465514633151567</t>
+  </si>
+  <si>
+    <t>JT5505607338561</t>
+  </si>
+  <si>
+    <t>9817961258666</t>
+  </si>
+  <si>
+    <t>465502961247710</t>
+  </si>
+  <si>
+    <t>YT8886715622217</t>
+  </si>
+  <si>
+    <t>YT7632553701941</t>
+  </si>
+  <si>
+    <t>YT7632865575296</t>
+  </si>
+  <si>
+    <t>465514489030346</t>
+  </si>
+  <si>
+    <t>777427085931458</t>
+  </si>
+  <si>
+    <t>465507914083094</t>
+  </si>
+  <si>
+    <t>79122173802535</t>
+  </si>
+  <si>
+    <t>YT8887474259342</t>
+  </si>
+  <si>
+    <t>9818042527494</t>
+  </si>
+  <si>
+    <t>777426842208139</t>
+  </si>
+  <si>
+    <t>JT5505842113414</t>
+  </si>
+  <si>
+    <t>9818049917828</t>
+  </si>
+  <si>
+    <t>9818058273226</t>
+  </si>
+  <si>
+    <t>79122934811109</t>
+  </si>
+  <si>
+    <t>79122687747282</t>
+  </si>
+  <si>
+    <t>465514247899696</t>
+  </si>
+  <si>
+    <t>777427186380345</t>
+  </si>
+  <si>
+    <t>YT8887499234380</t>
+  </si>
+  <si>
+    <t>JT5505044125581</t>
+  </si>
+  <si>
+    <t>79122847348936</t>
+  </si>
+  <si>
+    <t>777426933997095</t>
+  </si>
+  <si>
+    <t>465503371714135</t>
+  </si>
+  <si>
+    <t>JT5504948725054</t>
+  </si>
+  <si>
+    <t>79122602798414</t>
+  </si>
+  <si>
+    <t>465506370218522</t>
+  </si>
+  <si>
+    <t>JT5504898039627</t>
+  </si>
+  <si>
+    <t>8244401142220</t>
+  </si>
+  <si>
+    <t>465507898194276</t>
+  </si>
+  <si>
+    <t>777427144833852</t>
+  </si>
+  <si>
+    <t>JT5504948709547</t>
+  </si>
+  <si>
+    <t>JT5505554534455</t>
+  </si>
+  <si>
+    <t>465506538373629</t>
+  </si>
+  <si>
+    <t>465499311973338</t>
+  </si>
+  <si>
+    <t>777426918928394</t>
+  </si>
+  <si>
+    <t>JT5504985858847</t>
+  </si>
+  <si>
+    <t>435270971367024</t>
+  </si>
+  <si>
+    <t>465508083387532</t>
+  </si>
+  <si>
+    <t>465496611398797</t>
+  </si>
+  <si>
+    <t>79122903499256</t>
+  </si>
+  <si>
+    <t>YT8887233456818</t>
+  </si>
+  <si>
+    <t>9817995428423</t>
+  </si>
+  <si>
+    <t>465509360373029</t>
+  </si>
+  <si>
+    <t>465509132293841</t>
+  </si>
+  <si>
+    <t>YT8886995204480</t>
+  </si>
+  <si>
+    <t>777427404579120</t>
+  </si>
+  <si>
+    <t>YT8887110380694</t>
+  </si>
+  <si>
+    <t>JT5505579885426</t>
+  </si>
+  <si>
+    <t>JT3170316758166</t>
+  </si>
+  <si>
+    <t>79018771858616</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1799,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1051,6 +1813,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1059,8 +1824,221 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1356,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B458"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -2378,1885 +3356,2678 @@
         <v>50</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="4" t="s">
+    <row r="129" spans="1:1">
+      <c r="A129" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" s="6" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" s="6" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200" s="6" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" s="6" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202" s="6" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" s="4"/>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" s="4"/>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" s="4"/>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B129" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="4" t="s">
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B130" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="5" t="s">
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B131" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="5" t="s">
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B132" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="5" t="s">
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B133" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="5" t="s">
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B134" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="5" t="s">
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B135" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="4" t="s">
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B136" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="5" t="s">
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B137" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="5" t="s">
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B138" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="5" t="s">
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B139" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="4" t="s">
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B140" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" s="5" t="s">
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B141" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" s="4" t="s">
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B142" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" s="4" t="s">
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B143" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="5" t="s">
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B144" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="5" t="s">
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B145" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="5" t="s">
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B146" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="4" t="s">
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B147" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="4" t="s">
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B148" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="5" t="s">
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B149" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="5" t="s">
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B150" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="5" t="s">
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B151" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="5" t="s">
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B152" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="5" t="s">
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B153" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="4" t="s">
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B154" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="5" t="s">
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B155" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="5" t="s">
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B156" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="5" t="s">
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B157" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="5" t="s">
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B158" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="5" t="s">
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B159" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="4" t="s">
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B160" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="4" t="s">
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B161" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="5" t="s">
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B162" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="4" t="s">
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B163" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="5" t="s">
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B164" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="5" t="s">
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B165" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="5" t="s">
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B166" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="5" t="s">
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B167" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="5" t="s">
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B168" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="4" t="s">
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B169" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="5" t="s">
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B170" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="5" t="s">
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B171" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="5" t="s">
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B172" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="5" t="s">
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B173" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="5" t="s">
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B174" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="5" t="s">
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B175" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="5" t="s">
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B176" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="5" t="s">
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B177" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="4" t="s">
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B178" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="5" t="s">
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B179" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="4" t="s">
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B180" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="4" t="s">
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B181" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="4" t="s">
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B182" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="5" t="s">
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B183" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="5" t="s">
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B184" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="4" t="s">
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B185" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="5" t="s">
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B186" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="5" t="s">
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B187" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="5" t="s">
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B188" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="4" t="s">
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B189" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="4" t="s">
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B190" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="4" t="s">
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B191" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="5" t="s">
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B192" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="5" t="s">
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B193" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="5" t="s">
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B194" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="5" t="s">
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B195" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="5" t="s">
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B196" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="5" t="s">
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B197" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="4" t="s">
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B198" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="4" t="s">
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B199" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="5" t="s">
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B200" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="5" t="s">
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B201" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="5" t="s">
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B202" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="5" t="s">
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B203" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="4" t="s">
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B204" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B205" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B206" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B207" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B208" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B209" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" ht="15.6">
-      <c r="A210" s="3"/>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="1">
-        <v>777421971309997</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="1">
-        <v>79117952924235</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="1">
-        <v>465458300612210</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="1">
-        <v>465462997566968</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="A221" s="1">
-        <v>9817637752976</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="1">
-        <v>777422386231741</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" s="1">
-        <v>777422549883964</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" s="1">
-        <v>777422741197359</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" s="1">
-        <v>79117641603383</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" s="1">
-        <v>777422423684474</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" s="1">
-        <v>79117947325687</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" s="1">
-        <v>777422657466151</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" s="1">
-        <v>79118115286962</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" s="1">
-        <v>465458348367580</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" s="1">
-        <v>465464907314970</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" s="1">
-        <v>777422134424763</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" s="1">
-        <v>9817706152080</v>
-      </c>
-    </row>
-    <row r="245" spans="1:1">
-      <c r="A245" s="1">
-        <v>9817641420345</v>
-      </c>
-    </row>
-    <row r="246" spans="1:1">
-      <c r="A246" s="1">
-        <v>9817618218214</v>
-      </c>
-    </row>
-    <row r="247" spans="1:1">
-      <c r="A247" s="1">
-        <v>777422513725104</v>
-      </c>
-    </row>
-    <row r="248" spans="1:1">
-      <c r="A248" s="1">
-        <v>79118024749653</v>
-      </c>
-    </row>
-    <row r="249" spans="1:1">
-      <c r="A249" s="1">
-        <v>777422657905926</v>
-      </c>
-    </row>
-    <row r="250" spans="1:1">
-      <c r="A250" s="1">
-        <v>777423203000463</v>
-      </c>
-    </row>
-    <row r="251" spans="1:1">
-      <c r="A251" s="1">
-        <v>777422413035587</v>
-      </c>
-    </row>
-    <row r="252" spans="1:1">
-      <c r="A252" s="1">
-        <v>79117818077517</v>
-      </c>
-    </row>
-    <row r="253" spans="1:1">
-      <c r="A253" s="1">
-        <v>777422517419094</v>
-      </c>
-    </row>
-    <row r="254" spans="1:1">
-      <c r="A254" s="1">
-        <v>9817699670146</v>
-      </c>
-    </row>
-    <row r="255" spans="1:1">
-      <c r="A255" s="1">
-        <v>9817626176674</v>
-      </c>
-    </row>
-    <row r="256" spans="1:1">
-      <c r="A256" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="257" spans="1:1">
-      <c r="A257" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="258" spans="1:1">
-      <c r="A258" s="1">
-        <v>465464033007149</v>
-      </c>
-    </row>
-    <row r="259" spans="1:1">
-      <c r="A259" s="1">
-        <v>9817684175880</v>
-      </c>
-    </row>
-    <row r="260" spans="1:1">
-      <c r="A260" s="1">
-        <v>9817638532752</v>
-      </c>
-    </row>
-    <row r="261" spans="1:1">
-      <c r="A261" s="1">
-        <v>79117975994426</v>
-      </c>
-    </row>
-    <row r="262" spans="1:1">
-      <c r="A262" s="1">
-        <v>777422279037036</v>
-      </c>
-    </row>
-    <row r="263" spans="1:1">
-      <c r="A263" s="1">
-        <v>465460191668107</v>
-      </c>
-    </row>
-    <row r="264" spans="1:1">
-      <c r="A264" s="1">
-        <v>465458538755029</v>
-      </c>
-    </row>
-    <row r="265" spans="1:1">
-      <c r="A265" s="1">
-        <v>9817633727498</v>
-      </c>
-    </row>
-    <row r="266" spans="1:1">
-      <c r="A266" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="267" spans="1:1">
-      <c r="A267" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="268" spans="1:1">
-      <c r="A268" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="269" spans="1:1">
-      <c r="A269" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" s="1">
-        <v>79118367685893</v>
-      </c>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" s="1">
-        <v>9817700621226</v>
-      </c>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" s="1">
-        <v>79117796071346</v>
-      </c>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" s="1">
-        <v>465457962486311</v>
-      </c>
-    </row>
-    <row r="275" spans="1:1">
-      <c r="A275" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="276" spans="1:1">
-      <c r="A276" s="1">
-        <v>777422731528745</v>
-      </c>
-    </row>
-    <row r="277" spans="1:1">
-      <c r="A277" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="278" spans="1:1">
-      <c r="A278" s="1">
-        <v>465462045052132</v>
-      </c>
-    </row>
-    <row r="279" spans="1:1">
-      <c r="A279" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="280" spans="1:1">
-      <c r="A280" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="281" spans="1:1">
-      <c r="A281" s="1">
-        <v>777422556482984</v>
-      </c>
-    </row>
-    <row r="282" spans="1:1">
-      <c r="A282" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="283" spans="1:1">
-      <c r="A283" s="1">
-        <v>465464224986141</v>
-      </c>
-    </row>
-    <row r="284" spans="1:1">
-      <c r="A284" s="1">
-        <v>465461539296139</v>
-      </c>
-    </row>
-    <row r="285" spans="1:1">
-      <c r="A285" s="1">
-        <v>777422770801355</v>
-      </c>
-    </row>
-    <row r="286" spans="1:1">
-      <c r="A286" s="1" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="1">
-        <v>777423239248503</v>
-      </c>
+      <c r="A287" s="4"/>
     </row>
     <row r="288" spans="1:1">
-      <c r="A288" s="1">
-        <v>79117651536910</v>
-      </c>
+      <c r="A288" s="4"/>
     </row>
     <row r="289" spans="1:1">
-      <c r="A289" s="1">
-        <v>79117933681198</v>
+      <c r="A289" s="4" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="290" spans="1:1">
-      <c r="A290" s="1">
-        <v>9817627085660</v>
+      <c r="A290" s="6" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="291" spans="1:1">
-      <c r="A291" s="1">
-        <v>777422282995768</v>
+      <c r="A291" s="6" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="292" spans="1:1">
-      <c r="A292" s="1" t="s">
-        <v>162</v>
+      <c r="A292" s="6" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="1">
-        <v>777423239698605</v>
+      <c r="A293" s="4" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="294" spans="1:1">
-      <c r="A294" s="1">
-        <v>465465103750961</v>
+      <c r="A294" s="4" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" s="1">
-        <v>9817620085910</v>
+      <c r="A295" s="6" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="296" spans="1:1">
-      <c r="A296" s="1">
-        <v>465457413048475</v>
+      <c r="A296" s="6" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="297" spans="1:1">
-      <c r="A297" s="1">
-        <v>465456211470405</v>
+      <c r="A297" s="4" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="298" spans="1:1">
-      <c r="A298" s="1" t="s">
-        <v>163</v>
+      <c r="A298" s="6" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="299" spans="1:1">
-      <c r="A299" s="1">
-        <v>465464532957747</v>
+      <c r="A299" s="6" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="300" spans="1:1">
-      <c r="A300" s="1">
-        <v>777423140486346</v>
+      <c r="A300" s="6" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="301" spans="1:1">
-      <c r="A301" s="1" t="s">
-        <v>164</v>
+      <c r="A301" s="6" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="302" spans="1:1">
-      <c r="A302" s="1" t="s">
-        <v>165</v>
+      <c r="A302" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" s="4" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="304" spans="1:1">
-      <c r="A304" s="5" t="s">
-        <v>167</v>
+      <c r="A304" s="4" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="305" spans="1:1">
-      <c r="A305" s="5" t="s">
-        <v>168</v>
+      <c r="A305" s="4" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="4" t="s">
-        <v>169</v>
+        <v>340</v>
       </c>
     </row>
     <row r="307" spans="1:1">
-      <c r="A307" s="5" t="s">
-        <v>170</v>
+      <c r="A307" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="308" spans="1:1">
-      <c r="A308" s="5" t="s">
-        <v>171</v>
+      <c r="A308" s="4" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="5" t="s">
-        <v>172</v>
+      <c r="A309" s="6" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="310" spans="1:1">
-      <c r="A310" s="4" t="s">
-        <v>173</v>
+      <c r="A310" s="6" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" s="5" t="s">
-        <v>174</v>
+      <c r="A311" s="4" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="312" spans="1:1">
-      <c r="A312" s="5" t="s">
-        <v>175</v>
+      <c r="A312" s="4" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="313" spans="1:1">
-      <c r="A313" s="5" t="s">
-        <v>176</v>
+      <c r="A313" s="4" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="314" spans="1:1">
-      <c r="A314" s="4" t="s">
-        <v>177</v>
+      <c r="A314" s="6" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="315" spans="1:1">
-      <c r="A315" s="5" t="s">
-        <v>178</v>
+      <c r="A315" s="6" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="316" spans="1:1">
-      <c r="A316" s="5" t="s">
-        <v>179</v>
+      <c r="A316" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="317" spans="1:1">
-      <c r="A317" s="5" t="s">
-        <v>180</v>
+      <c r="A317" s="6" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="318" spans="1:1">
-      <c r="A318" s="5" t="s">
-        <v>181</v>
+      <c r="A318" s="6" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="319" spans="1:1">
-      <c r="A319" s="5" t="s">
-        <v>182</v>
+      <c r="A319" s="4" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="320" spans="1:1">
-      <c r="A320" s="5" t="s">
-        <v>183</v>
+      <c r="A320" s="6" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="321" spans="1:1">
-      <c r="A321" s="5" t="s">
-        <v>184</v>
+      <c r="A321" s="6" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="322" spans="1:1">
-      <c r="A322" s="4" t="s">
-        <v>185</v>
+      <c r="A322" s="6" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="323" spans="1:1">
-      <c r="A323" s="5" t="s">
-        <v>186</v>
+      <c r="A323" s="4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="324" spans="1:1">
-      <c r="A324" s="5" t="s">
-        <v>187</v>
+      <c r="A324" s="4" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="325" spans="1:1">
-      <c r="A325" s="4" t="s">
-        <v>188</v>
+      <c r="A325" s="6" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="326" spans="1:1">
-      <c r="A326" s="5" t="s">
-        <v>189</v>
+      <c r="A326" s="6" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="327" spans="1:1">
-      <c r="A327" s="5" t="s">
-        <v>190</v>
+      <c r="A327" s="4" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="328" spans="1:1">
-      <c r="A328" s="4" t="s">
-        <v>191</v>
+      <c r="A328" s="6" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="4" t="s">
-        <v>192</v>
+      <c r="A329" s="6" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="330" spans="1:1">
-      <c r="A330" s="5" t="s">
-        <v>193</v>
+      <c r="A330" s="6" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="331" spans="1:1">
-      <c r="A331" s="5" t="s">
-        <v>194</v>
+      <c r="A331" s="6" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="332" spans="1:1">
-      <c r="A332" s="4" t="s">
-        <v>195</v>
+      <c r="A332" s="6" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="333" spans="1:1">
-      <c r="A333" s="5" t="s">
-        <v>196</v>
+      <c r="A333" s="6" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="334" spans="1:1">
-      <c r="A334" s="5" t="s">
-        <v>197</v>
+      <c r="A334" s="4" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="335" spans="1:1">
-      <c r="A335" s="5" t="s">
-        <v>198</v>
+      <c r="A335" s="6" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="336" spans="1:1">
-      <c r="A336" s="5" t="s">
-        <v>199</v>
+      <c r="A336" s="4" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" s="4" t="s">
-        <v>200</v>
+        <v>370</v>
       </c>
     </row>
     <row r="338" spans="1:1">
-      <c r="A338" s="5" t="s">
-        <v>201</v>
+      <c r="A338" s="6" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" s="4" t="s">
-        <v>202</v>
+        <v>372</v>
       </c>
     </row>
     <row r="340" spans="1:1">
-      <c r="A340" s="5" t="s">
-        <v>203</v>
+      <c r="A340" s="6" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="341" spans="1:1">
-      <c r="A341" s="5" t="s">
-        <v>204</v>
+      <c r="A341" s="6" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="342" spans="1:1">
-      <c r="A342" s="4" t="s">
-        <v>205</v>
+      <c r="A342" s="6" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="343" spans="1:1">
-      <c r="A343" s="5" t="s">
-        <v>206</v>
+      <c r="A343" s="6" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="344" spans="1:1">
-      <c r="A344" s="5" t="s">
-        <v>207</v>
+      <c r="A344" s="6" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="345" spans="1:1">
-      <c r="A345" s="5" t="s">
-        <v>208</v>
+      <c r="A345" s="6" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="346" spans="1:1">
-      <c r="A346" s="5" t="s">
-        <v>209</v>
+      <c r="A346" s="6" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="347" spans="1:1">
-      <c r="A347" s="5" t="s">
-        <v>210</v>
+      <c r="A347" s="6" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="348" spans="1:1">
-      <c r="A348" s="4" t="s">
-        <v>211</v>
+      <c r="A348" s="6" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="349" spans="1:1">
-      <c r="A349" s="5" t="s">
-        <v>212</v>
+      <c r="A349" s="6" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="350" spans="1:1">
-      <c r="A350" s="5" t="s">
-        <v>213</v>
+      <c r="A350" s="4" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="351" spans="1:1">
-      <c r="A351" s="4" t="s">
-        <v>214</v>
+      <c r="A351" s="6" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="352" spans="1:1">
-      <c r="A352" s="4" t="s">
-        <v>215</v>
+      <c r="A352" s="6" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="353" spans="1:1">
-      <c r="A353" s="5" t="s">
-        <v>216</v>
+      <c r="A353" s="6" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="354" spans="1:1">
-      <c r="A354" s="5" t="s">
-        <v>217</v>
+      <c r="A354" s="6" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="355" spans="1:1">
       <c r="A355" s="4" t="s">
-        <v>218</v>
+        <v>388</v>
       </c>
     </row>
     <row r="356" spans="1:1">
-      <c r="A356" s="4" t="s">
-        <v>219</v>
+      <c r="A356" s="6" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="357" spans="1:1">
-      <c r="A357" s="5" t="s">
-        <v>220</v>
+      <c r="A357" s="4" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="358" spans="1:1">
       <c r="A358" s="4" t="s">
-        <v>221</v>
+        <v>391</v>
       </c>
     </row>
     <row r="359" spans="1:1">
-      <c r="A359" s="5" t="s">
-        <v>222</v>
+      <c r="A359" s="6" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="360" spans="1:1">
       <c r="A360" s="4" t="s">
-        <v>223</v>
+        <v>393</v>
       </c>
     </row>
     <row r="361" spans="1:1">
-      <c r="A361" s="5" t="s">
-        <v>224</v>
+      <c r="A361" s="4" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="362" spans="1:1">
-      <c r="A362" s="5" t="s">
-        <v>225</v>
+      <c r="A362" s="6" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="363" spans="1:1">
-      <c r="A363" s="5" t="s">
-        <v>226</v>
+      <c r="A363" s="6" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="364" spans="1:1">
       <c r="A364" s="4" t="s">
-        <v>227</v>
+        <v>397</v>
       </c>
     </row>
     <row r="365" spans="1:1">
-      <c r="A365" s="5" t="s">
-        <v>228</v>
+      <c r="A365" s="4" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="366" spans="1:1">
-      <c r="A366" s="5" t="s">
-        <v>229</v>
+      <c r="A366" s="6" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="367" spans="1:1">
-      <c r="A367" s="5" t="s">
-        <v>230</v>
+      <c r="A367" s="6" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="368" spans="1:1">
-      <c r="A368" s="4" t="s">
-        <v>231</v>
+      <c r="A368" s="6" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="369" spans="1:1">
-      <c r="A369" s="4" t="s">
-        <v>232</v>
+      <c r="A369" s="6" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="370" spans="1:1">
-      <c r="A370" s="5" t="s">
-        <v>233</v>
+      <c r="A370" s="6" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="371" spans="1:1">
-      <c r="A371" s="5" t="s">
-        <v>234</v>
+      <c r="A371" s="6" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="372" spans="1:1">
-      <c r="A372" s="5" t="s">
-        <v>235</v>
+      <c r="A372" s="4" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="373" spans="1:1">
-      <c r="A373" s="5" t="s">
-        <v>236</v>
+      <c r="A373" s="6" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="374" spans="1:1">
-      <c r="A374" s="5" t="s">
-        <v>237</v>
+      <c r="A374" s="6" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="375" spans="1:1">
-      <c r="A375" s="4" t="s">
-        <v>238</v>
+      <c r="A375" s="6" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="376" spans="1:1">
-      <c r="A376" s="5" t="s">
-        <v>239</v>
+      <c r="A376" s="6" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="377" spans="1:1">
-      <c r="A377" s="5" t="s">
-        <v>240</v>
+      <c r="A377" s="6" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="378" spans="1:1">
-      <c r="A378" s="5" t="s">
-        <v>241</v>
+      <c r="A378" s="4" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" s="4" t="s">
-        <v>242</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" s="4" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="381" spans="1:1">
-      <c r="A381" s="5" t="s">
-        <v>243</v>
+      <c r="A381" s="6" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="382" spans="1:1">
-      <c r="A382" s="4" t="s">
-        <v>244</v>
+      <c r="A382" s="6" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="383" spans="1:1">
-      <c r="A383" s="4" t="s">
-        <v>245</v>
+      <c r="A383" s="6" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="384" spans="1:1">
-      <c r="A384" s="4" t="s">
-        <v>246</v>
+      <c r="A384" s="6" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="385" spans="1:1">
-      <c r="A385" s="5" t="s">
-        <v>247</v>
+      <c r="A385" s="4" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="386" spans="1:1">
-      <c r="A386" s="5" t="s">
-        <v>248</v>
+      <c r="A386" s="4" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="387" spans="1:1">
-      <c r="A387" s="5" t="s">
-        <v>249</v>
+      <c r="A387" s="6" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="388" spans="1:1">
-      <c r="A388" s="5" t="s">
-        <v>250</v>
+      <c r="A388" s="6" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="389" spans="1:1">
-      <c r="A389" s="5" t="s">
-        <v>247</v>
+      <c r="A389" s="6" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="390" spans="1:1">
-      <c r="A390" s="5" t="s">
-        <v>251</v>
+      <c r="A390" s="6" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="391" spans="1:1">
-      <c r="A391" s="4" t="s">
-        <v>252</v>
+      <c r="A391" s="6" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="392" spans="1:1">
-      <c r="A392" s="5" t="s">
-        <v>253</v>
+      <c r="A392" s="6" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="393" spans="1:1">
-      <c r="A393" s="5" t="s">
-        <v>253</v>
+      <c r="A393" s="6" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="394" spans="1:1">
-      <c r="A394" s="5" t="s">
-        <v>254</v>
+      <c r="A394" s="4" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="395" spans="1:1">
-      <c r="A395" s="5" t="s">
-        <v>255</v>
+      <c r="A395" s="4" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="396" spans="1:1">
-      <c r="A396" s="5" t="s">
-        <v>256</v>
+      <c r="A396" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="397" spans="1:1">
-      <c r="A397" s="4" t="s">
-        <v>257</v>
+      <c r="A397" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="398" spans="1:1">
-      <c r="A398" s="5" t="s">
-        <v>258</v>
+      <c r="A398" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="399" spans="1:1">
-      <c r="A399" s="4" t="s">
-        <v>259</v>
+      <c r="A399" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="400" spans="1:1">
-      <c r="A400" s="4" t="s">
-        <v>260</v>
+      <c r="A400" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="401" spans="1:1">
-      <c r="A401" s="5" t="s">
-        <v>261</v>
+      <c r="A401" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="402" spans="1:1">
-      <c r="A402" s="5" t="s">
-        <v>262</v>
+      <c r="A402" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="403" spans="1:1">
-      <c r="A403" s="4" t="s">
-        <v>263</v>
+      <c r="A403" s="6" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" s="4" t="s">
-        <v>264</v>
+        <v>211</v>
       </c>
     </row>
     <row r="405" spans="1:1">
-      <c r="A405" s="5" t="s">
-        <v>265</v>
+      <c r="A405" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="406" spans="1:1">
-      <c r="A406" s="4" t="s">
-        <v>266</v>
+      <c r="A406" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="407" spans="1:1">
-      <c r="A407" s="4" t="s">
-        <v>267</v>
+      <c r="A407" s="6" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="408" spans="1:1">
-      <c r="A408" s="4" t="s">
-        <v>268</v>
+      <c r="A408" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="409" spans="1:1">
-      <c r="A409" s="4" t="s">
-        <v>269</v>
+      <c r="A409" s="6" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="410" spans="1:1">
-      <c r="A410" s="5" t="s">
-        <v>270</v>
+      <c r="A410" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" s="4" t="s">
-        <v>271</v>
+        <v>218</v>
       </c>
     </row>
     <row r="412" spans="1:1">
-      <c r="A412" s="5" t="s">
-        <v>272</v>
+      <c r="A412" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="413" spans="1:1">
-      <c r="A413" s="5" t="s">
-        <v>273</v>
+      <c r="A413" s="6" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="414" spans="1:1">
-      <c r="A414" s="5" t="s">
-        <v>274</v>
+      <c r="A414" s="4" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="415" spans="1:1">
-      <c r="A415" s="5" t="s">
-        <v>275</v>
+      <c r="A415" s="6" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="416" spans="1:1">
-      <c r="A416" s="5" t="s">
-        <v>276</v>
+      <c r="A416" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="417" spans="1:1">
-      <c r="A417" s="5" t="s">
-        <v>277</v>
+      <c r="A417" s="6" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="418" spans="1:1">
-      <c r="A418" s="5" t="s">
-        <v>278</v>
+      <c r="A418" s="4" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="419" spans="1:1">
-      <c r="A419" s="5" t="s">
-        <v>279</v>
+      <c r="A419" s="6" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="420" spans="1:1">
-      <c r="A420" s="5" t="s">
-        <v>280</v>
+      <c r="A420" s="4" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="421" spans="1:1">
-      <c r="A421" s="5" t="s">
-        <v>281</v>
+      <c r="A421" s="4" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="422" spans="1:1">
-      <c r="A422" s="5" t="s">
-        <v>282</v>
+      <c r="A422" s="4" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="423" spans="1:1">
-      <c r="A423" s="5" t="s">
-        <v>283</v>
+      <c r="A423" s="6" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="424" spans="1:1">
-      <c r="A424" s="5" t="s">
-        <v>284</v>
+      <c r="A424" s="4" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="425" spans="1:1">
-      <c r="A425" s="5" t="s">
-        <v>285</v>
+      <c r="A425" s="4" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="426" spans="1:1">
-      <c r="A426" s="5" t="s">
-        <v>286</v>
+      <c r="A426" s="4" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="427" spans="1:1">
-      <c r="A427" s="5" t="s">
-        <v>287</v>
+      <c r="A427" s="6" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="428" spans="1:1">
-      <c r="A428" s="5" t="s">
-        <v>288</v>
+      <c r="A428" s="4" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" s="4" t="s">
-        <v>289</v>
+        <v>236</v>
       </c>
     </row>
     <row r="430" spans="1:1">
-      <c r="A430" s="4" t="s">
-        <v>290</v>
+      <c r="A430" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="431" spans="1:1">
-      <c r="A431" s="5" t="s">
-        <v>291</v>
+      <c r="A431" s="4" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="432" spans="1:1">
-      <c r="A432" s="5" t="s">
-        <v>292</v>
+      <c r="A432" s="4" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="433" spans="1:1">
-      <c r="A433" s="4" t="s">
-        <v>293</v>
+      <c r="A433" s="6" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="434" spans="1:1">
-      <c r="A434" s="5" t="s">
-        <v>294</v>
+      <c r="A434" s="6" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="435" spans="1:1">
-      <c r="A435" s="4" t="s">
-        <v>295</v>
+      <c r="A435" s="6" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" s="4" t="s">
-        <v>296</v>
+        <v>243</v>
       </c>
     </row>
     <row r="437" spans="1:1">
-      <c r="A437" s="5" t="s">
-        <v>297</v>
+      <c r="A437" s="4" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="438" spans="1:1">
       <c r="A438" s="4" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
     </row>
     <row r="439" spans="1:1">
-      <c r="A439" s="5" t="s">
-        <v>299</v>
+      <c r="A439" s="6" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="440" spans="1:1">
-      <c r="A440" s="4" t="s">
-        <v>300</v>
+      <c r="A440" s="6" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="441" spans="1:1">
-      <c r="A441" s="4" t="s">
-        <v>301</v>
+      <c r="A441" s="6" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="442" spans="1:1">
       <c r="A442" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1">
+      <c r="A443" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1">
+      <c r="A444" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1">
+      <c r="A445" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1">
+      <c r="A446" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1">
+      <c r="A447" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1">
+      <c r="A448" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="449" spans="1:1">
+      <c r="A449" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="450" spans="1:1">
+      <c r="A450" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="451" spans="1:1">
+      <c r="A451" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="452" spans="1:1">
+      <c r="A452" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="453" spans="1:1">
+      <c r="A453" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="454" spans="1:1">
+      <c r="A454" s="6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="455" spans="1:1">
+      <c r="A455" s="6" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="456" spans="1:1">
+      <c r="A456" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="457" spans="1:1">
+      <c r="A457" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="458" spans="1:1">
+      <c r="A458" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="459" spans="1:1">
+      <c r="A459" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="460" spans="1:1">
+      <c r="A460" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="461" spans="1:1">
+      <c r="A461" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="462" spans="1:1">
+      <c r="A462" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="463" spans="1:1">
+      <c r="A463" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="464" spans="1:1">
+      <c r="A464" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="465" spans="1:1">
+      <c r="A465" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="466" spans="1:1">
+      <c r="A466" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="467" spans="1:1">
+      <c r="A467" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="468" spans="1:1">
+      <c r="A468" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="469" spans="1:1">
+      <c r="A469" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="470" spans="1:1">
+      <c r="A470" s="4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="471" spans="1:1">
+      <c r="A471" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="472" spans="1:1">
+      <c r="A472" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="473" spans="1:1">
+      <c r="A473" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="474" spans="1:1">
+      <c r="A474" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="475" spans="1:1">
+      <c r="A475" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="476" spans="1:1">
+      <c r="A476" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="477" spans="1:1">
+      <c r="A477" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="478" spans="1:1">
+      <c r="A478" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="479" spans="1:1">
+      <c r="A479" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="480" spans="1:1">
+      <c r="A480" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="481" spans="1:1">
+      <c r="A481" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="482" spans="1:1">
+      <c r="A482" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="483" spans="1:1">
+      <c r="A483" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="484" spans="1:1">
+      <c r="A484" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="485" spans="1:1">
+      <c r="A485" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="486" spans="1:1">
+      <c r="A486" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="487" spans="1:1">
+      <c r="A487" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="488" spans="1:1">
+      <c r="A488" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="489" spans="1:1">
+      <c r="A489" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="490" spans="1:1">
+      <c r="A490" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="491" spans="1:1">
+      <c r="A491" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="492" spans="1:1">
+      <c r="A492" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="493" spans="1:1">
+      <c r="A493" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="494" spans="1:1">
+      <c r="A494" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="495" spans="1:1">
+      <c r="A495" s="6" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="443" spans="1:1">
-      <c r="A443" s="4" t="s">
+    <row r="496" spans="1:1">
+      <c r="A496" s="6" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="444" spans="1:1">
-      <c r="A444" s="5" t="s">
+    <row r="497" spans="1:1">
+      <c r="A497" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="445" spans="1:1">
-      <c r="A445" s="4" t="s">
+    <row r="498" spans="1:1">
+      <c r="A498" s="6" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="446" spans="1:1">
-      <c r="A446" s="5" t="s">
+    <row r="499" spans="1:1">
+      <c r="A499" s="6" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="447" spans="1:1">
-      <c r="A447" s="5" t="s">
+    <row r="500" spans="1:1">
+      <c r="A500" s="6" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="448" spans="1:1">
-      <c r="A448" s="5" t="s">
+    <row r="501" spans="1:1">
+      <c r="A501" s="6" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="449" spans="1:1">
-      <c r="A449" s="5" t="s">
+    <row r="502" spans="1:1">
+      <c r="A502" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="450" spans="1:1">
-      <c r="A450" s="5" t="s">
+    <row r="503" spans="1:1">
+      <c r="A503" s="6" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="451" spans="1:1">
-      <c r="A451" s="5" t="s">
+    <row r="504" spans="1:1">
+      <c r="A504" s="4" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="452" spans="1:1">
-      <c r="A452" s="5" t="s">
+    <row r="505" spans="1:1">
+      <c r="A505" s="6" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="453" spans="1:1">
-      <c r="A453" s="5" t="s">
+    <row r="506" spans="1:1">
+      <c r="A506" s="6" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="454" spans="1:1">
-      <c r="A454" s="5" t="s">
+    <row r="507" spans="1:1">
+      <c r="A507" s="6" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="455" spans="1:1">
-      <c r="A455" s="4" t="s">
+    <row r="508" spans="1:1">
+      <c r="A508" s="6" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="456" spans="1:1">
-      <c r="A456" s="5" t="s">
+    <row r="509" spans="1:1">
+      <c r="A509" s="6" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="457" spans="1:1">
-      <c r="A457" s="5" t="s">
+    <row r="510" spans="1:1">
+      <c r="A510" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="458" spans="1:1">
-      <c r="A458" s="5" t="s">
-        <v>270</v>
+    <row r="511" spans="1:1">
+      <c r="A511" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="512" spans="1:1">
+      <c r="A512" s="6" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="513" spans="1:1">
+      <c r="A513" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="514" spans="1:1">
+      <c r="A514" s="6" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="515" spans="1:1">
+      <c r="A515" s="6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="516" spans="1:1">
+      <c r="A516" s="4"/>
+    </row>
+    <row r="517" spans="1:1">
+      <c r="A517" s="4"/>
+    </row>
+    <row r="518" spans="1:1">
+      <c r="A518" s="4"/>
+    </row>
+    <row r="519" spans="1:1">
+      <c r="A519" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="520" spans="1:1">
+      <c r="A520" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="521" spans="1:1">
+      <c r="A521" s="6" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="522" spans="1:1">
+      <c r="A522" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="523" spans="1:1">
+      <c r="A523" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="524" spans="1:1">
+      <c r="A524" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="525" spans="1:1">
+      <c r="A525" s="6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="526" spans="1:1">
+      <c r="A526" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="527" spans="1:1">
+      <c r="A527" s="6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="528" spans="1:1">
+      <c r="A528" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="529" spans="1:1">
+      <c r="A529" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="530" spans="1:1">
+      <c r="A530" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="531" spans="1:1">
+      <c r="A531" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="532" spans="1:1">
+      <c r="A532" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="533" spans="1:1">
+      <c r="A533" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="534" spans="1:1">
+      <c r="A534" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="535" spans="1:1">
+      <c r="A535" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="536" spans="1:1">
+      <c r="A536" s="6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="537" spans="1:1">
+      <c r="A537" s="6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="538" spans="1:1">
+      <c r="A538" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="539" spans="1:1">
+      <c r="A539" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="540" spans="1:1">
+      <c r="A540" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="541" spans="1:1">
+      <c r="A541" s="6" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="542" spans="1:1">
+      <c r="A542" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="543" spans="1:1">
+      <c r="A543" s="6" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="544" spans="1:1">
+      <c r="A544" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="545" spans="1:1">
+      <c r="A545" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="546" spans="1:1">
+      <c r="A546" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="547" spans="1:1">
+      <c r="A547" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="548" spans="1:1">
+      <c r="A548" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="549" spans="1:1">
+      <c r="A549" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="550" spans="1:1">
+      <c r="A550" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="551" spans="1:1">
+      <c r="A551" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="552" spans="1:1">
+      <c r="A552" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="553" spans="1:1">
+      <c r="A553" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="554" spans="1:1">
+      <c r="A554" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="555" spans="1:1">
+      <c r="A555" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="556" spans="1:1">
+      <c r="A556" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="557" spans="1:1">
+      <c r="A557" s="6" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="558" spans="1:1">
+      <c r="A558" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="559" spans="1:1">
+      <c r="A559" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="560" spans="1:1">
+      <c r="A560" s="6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="561" spans="1:1">
+      <c r="A561" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="562" spans="1:1">
+      <c r="A562" s="6" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="563" spans="1:1">
+      <c r="A563" s="6" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="564" spans="1:1">
+      <c r="A564" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1">
+      <c r="A565" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="566" spans="1:1">
+      <c r="A566" s="6" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1">
+      <c r="A567" s="6" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1">
+      <c r="A568" s="6" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1">
+      <c r="A569" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1">
+      <c r="A570" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1">
+      <c r="A571" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="572" spans="1:1">
+      <c r="A572" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1">
+      <c r="A573" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1">
+      <c r="A574" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1">
+      <c r="A575" s="6" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="576" spans="1:1">
+      <c r="A576" s="6" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1">
+      <c r="A577" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="578" spans="1:1">
+      <c r="A578" s="6" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1">
+      <c r="A579" s="6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1">
+      <c r="A580" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1">
+      <c r="A581" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1">
+      <c r="A582" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1">
+      <c r="A583" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="584" spans="1:1">
+      <c r="A584" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1">
+      <c r="A585" s="6" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1">
+      <c r="A586" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1">
+      <c r="A587" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="588" spans="1:1">
+      <c r="A588" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1">
+      <c r="A589" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="590" spans="1:1">
+      <c r="A590" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1">
+      <c r="A591" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1">
+      <c r="A592" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1">
+      <c r="A593" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1">
+      <c r="A594" s="4" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1">
+      <c r="A595" s="4" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1">
+      <c r="A596" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1">
+      <c r="A597" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1">
+      <c r="A598" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1">
+      <c r="A599" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1">
+      <c r="A600" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1">
+      <c r="A601" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1">
+      <c r="A602" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1">
+      <c r="A603" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1">
+      <c r="A604" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1">
+      <c r="A605" s="6" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1">
+      <c r="A606" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1">
+      <c r="A607" s="4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1">
+      <c r="A608" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1">
+      <c r="A609" s="4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1">
+      <c r="A610" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1">
+      <c r="A611" s="6" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1">
+      <c r="A612" s="4" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1">
+      <c r="A613" s="6" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1">
+      <c r="A614" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1">
+      <c r="A615" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1">
+      <c r="A616" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1">
+      <c r="A617" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1">
+      <c r="A618" s="6" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1">
+      <c r="A619" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1">
+      <c r="A620" s="6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1">
+      <c r="A621" s="6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1">
+      <c r="A622" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1">
+      <c r="A623" s="6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1">
+      <c r="A624" s="6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1">
+      <c r="A625" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1">
+      <c r="A626" s="6" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1">
+      <c r="A627" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1">
+      <c r="A628" s="6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1">
+      <c r="A629" s="6" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1">
+      <c r="A630" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1">
+      <c r="A631" s="6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1">
+      <c r="A632" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1">
+      <c r="A633" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1">
+      <c r="A634" s="6" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1">
+      <c r="A635" s="6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1">
+      <c r="A636" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1">
+      <c r="A637" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1">
+      <c r="A638" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1">
+      <c r="A639" s="6" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1">
+      <c r="A640" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1">
+      <c r="A641" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1">
+      <c r="A642" s="6" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1">
+      <c r="A643" s="6" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1">
+      <c r="A644" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1">
+      <c r="A645" s="6" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1">
+      <c r="A646" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1">
+      <c r="A647" s="4" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1">
+      <c r="A648" s="4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1">
+      <c r="A649" s="6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1">
+      <c r="A650" s="6" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1">
+      <c r="A651" s="6" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1">
+      <c r="A652" s="4" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1">
+      <c r="A653" s="6" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1">
+      <c r="A654" s="6" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1">
+      <c r="A655" s="6" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1">
+      <c r="A656" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1">
+      <c r="A657" s="4" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1">
+      <c r="A658" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1">
+      <c r="A659" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1">
+      <c r="A660" s="6" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1">
+      <c r="A661" s="4" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1">
+      <c r="A662" s="6" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1">
+      <c r="A663" s="4" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1">
+      <c r="A664" s="4" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1">
+      <c r="A665" s="4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1">
+      <c r="A666" s="6" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
